--- a/Delovni listi/Rezultati-izpita.xlsx
+++ b/Delovni listi/Rezultati-izpita.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\janka\OneDrive\Namizje\SŠ - MAT\Matematika-v-srednjem-strokovnem-izobrazevanju\Delovni listi\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/27bd894ee34b290c/Namizje/SŠ - MAT/Matematika-v-srednjem-strokovnem-izobrazevanju/Delovni listi/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CD91D17-1B0A-4540-AF2F-4FA765BCD066}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-3405" windowWidth="29040" windowHeight="15720" xr2:uid="{5FB633E4-0CB3-431C-99E0-CA746FECD604}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5FB633E4-0CB3-431C-99E0-CA746FECD604}"/>
   </bookViews>
   <sheets>
     <sheet name="Podatki" sheetId="1" r:id="rId1"/>
@@ -25,16 +25,12 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Podatki!$A$2:$S$117</definedName>
     <definedName name="_xlchart.v1.0" hidden="1">Podatki!$N$2</definedName>
     <definedName name="_xlchart.v1.1" hidden="1">Podatki!$N$3:$N$117</definedName>
-    <definedName name="_xlchart.v1.10" hidden="1">Podatki!$Q$2</definedName>
-    <definedName name="_xlchart.v1.11" hidden="1">Podatki!$Q$3:$Q$117</definedName>
     <definedName name="_xlchart.v1.2" hidden="1">Podatki!$O$2</definedName>
     <definedName name="_xlchart.v1.3" hidden="1">Podatki!$O$3:$O$117</definedName>
-    <definedName name="_xlchart.v1.4" hidden="1">Podatki!$Q$2</definedName>
-    <definedName name="_xlchart.v1.5" hidden="1">Podatki!$Q$3:$Q$117</definedName>
-    <definedName name="_xlchart.v1.6" hidden="1">Podatki!$N$2</definedName>
-    <definedName name="_xlchart.v1.7" hidden="1">Podatki!$N$3:$N$117</definedName>
-    <definedName name="_xlchart.v1.8" hidden="1">Podatki!$O$2</definedName>
-    <definedName name="_xlchart.v1.9" hidden="1">Podatki!$O$3:$O$117</definedName>
+    <definedName name="_xlchart.v1.4" hidden="1">Podatki!$N$2</definedName>
+    <definedName name="_xlchart.v1.5" hidden="1">Podatki!$N$3:$N$117</definedName>
+    <definedName name="_xlchart.v1.6" hidden="1">Podatki!$O$2</definedName>
+    <definedName name="_xlchart.v1.7" hidden="1">Podatki!$O$3:$O$117</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -68,7 +64,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -565,7 +561,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="169" formatCode="0.0"/>
+    <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -744,6 +740,7 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -756,7 +753,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Navadno" xfId="0" builtinId="0"/>
@@ -845,7 +841,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="sl-SI"/>
+          <a:endParaRPr lang="en-US"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -1638,6 +1634,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1645,7 +1642,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1745,7 +1741,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="sl-SI"/>
+          <a:endParaRPr lang="en-US"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -5405,7 +5401,7 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:absoluteAnchor>
     <xdr:pos x="0" y="0"/>
-    <xdr:ext cx="9297051" cy="6073205"/>
+    <xdr:ext cx="9297412" cy="6069027"/>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="Grafikon 1">
@@ -5438,7 +5434,7 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:absoluteAnchor>
     <xdr:pos x="0" y="0"/>
-    <xdr:ext cx="9297051" cy="6073205"/>
+    <xdr:ext cx="9297412" cy="6069027"/>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="Grafikon 1">
@@ -5471,7 +5467,7 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:absoluteAnchor>
     <xdr:pos x="0" y="0"/>
-    <xdr:ext cx="9297051" cy="6073205"/>
+    <xdr:ext cx="9297412" cy="6069027"/>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="Grafikon 1">
@@ -5504,7 +5500,7 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:absoluteAnchor>
     <xdr:pos x="0" y="0"/>
-    <xdr:ext cx="9305192" cy="6081346"/>
+    <xdr:ext cx="9297412" cy="6069027"/>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" Requires="cx1">
         <xdr:graphicFrame macro="">
@@ -5570,7 +5566,7 @@
         <cdr:cNvPr id="2" name="Pravokotnik 1">
           <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3F108AD0-9045-2553-4CFC-7A5E9D247318}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1FAC607B-3383-A9F5-510B-592CB994F51F}"/>
             </a:ext>
           </a:extLst>
         </cdr:cNvPr>
@@ -5581,7 +5577,7 @@
       <cdr:spPr>
         <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="0" y="0"/>
-          <a:ext cx="9305192" cy="6081346"/>
+          <a:ext cx="9297412" cy="6069027"/>
         </a:xfrm>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <a:avLst/>
@@ -5615,7 +5611,7 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:absoluteAnchor>
     <xdr:pos x="0" y="0"/>
-    <xdr:ext cx="9305192" cy="6081346"/>
+    <xdr:ext cx="9297412" cy="6069027"/>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="Grafikon 1">
@@ -5967,37 +5963,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="19" t="s">
         <v>85</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18" t="s">
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19" t="s">
         <v>86</v>
       </c>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
-      <c r="I1" s="18"/>
-      <c r="J1" s="18"/>
-      <c r="K1" s="18"/>
-      <c r="L1" s="18"/>
-      <c r="M1" s="18"/>
-      <c r="N1" s="18" t="s">
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+      <c r="I1" s="19"/>
+      <c r="J1" s="19"/>
+      <c r="K1" s="19"/>
+      <c r="L1" s="19"/>
+      <c r="M1" s="19"/>
+      <c r="N1" s="19" t="s">
         <v>87</v>
       </c>
-      <c r="O1" s="18"/>
-      <c r="P1" s="18" t="s">
+      <c r="O1" s="19"/>
+      <c r="P1" s="19" t="s">
         <v>105</v>
       </c>
-      <c r="Q1" s="18"/>
-      <c r="R1" s="18"/>
-      <c r="S1" s="18"/>
-      <c r="U1" s="17" t="s">
+      <c r="Q1" s="19"/>
+      <c r="R1" s="19"/>
+      <c r="S1" s="19"/>
+      <c r="U1" s="18" t="s">
         <v>106</v>
       </c>
-      <c r="V1" s="17"/>
+      <c r="V1" s="18"/>
     </row>
     <row r="2" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="9" t="s">
@@ -6108,19 +6104,19 @@
         <v>5</v>
       </c>
       <c r="P3" s="7">
-        <f>IF(COUNTBLANK(D3:M3)=10,"",SUM(D3:M3))</f>
+        <f t="shared" ref="P3:P9" si="0">IF(COUNTBLANK(D3:M3)=10,"",SUM(D3:M3))</f>
         <v>2</v>
       </c>
       <c r="Q3" s="7">
-        <f>IF(COUNTBLANK(D3:O3)=12,"",MAX(N3+P3,O3+0.5*P3))</f>
+        <f t="shared" ref="Q3:Q34" si="1">IF(COUNTBLANK(D3:O3)=12,"",MAX(N3+P3,O3+0.5*P3))</f>
         <v>7</v>
       </c>
       <c r="R3" s="8">
-        <f>IF(COUNTBLANK(N3:O3)=2,"",IF(AND(SUM(N3:O3)=0,P3&lt;0),0,Q3/100))</f>
+        <f t="shared" ref="R3:R34" si="2">IF(COUNTBLANK(N3:O3)=2,"",IF(AND(SUM(N3:O3)=0,P3&lt;0),0,Q3/100))</f>
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="S3" s="7" t="str">
-        <f>IF(R3="","ni opravljal izpita",IF(R3&lt;$U$3,"negativno",LOOKUP(R3,$U$3:$U$7,$V$3:$V$7)))</f>
+        <f t="shared" ref="S3:S34" si="3">IF(R3="","ni opravljal izpita",IF(R3&lt;$U$3,"negativno",LOOKUP(R3,$U$3:$U$7,$V$3:$V$7)))</f>
         <v>negativno</v>
       </c>
       <c r="U3" s="2">
@@ -6163,19 +6159,19 @@
       </c>
       <c r="O4" s="3"/>
       <c r="P4" s="7">
-        <f>IF(COUNTBLANK(D4:M4)=10,"",SUM(D4:M4))</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="Q4" s="7">
-        <f>IF(COUNTBLANK(D4:O4)=12,"",MAX(N4+P4,O4+0.5*P4))</f>
+        <f t="shared" si="1"/>
         <v>66</v>
       </c>
       <c r="R4" s="8">
-        <f>IF(COUNTBLANK(N4:O4)=2,"",IF(AND(SUM(N4:O4)=0,P4&lt;0),0,Q4/100))</f>
+        <f t="shared" si="2"/>
         <v>0.66</v>
       </c>
       <c r="S4" s="7">
-        <f>IF(R4="","ni opravljal izpita",IF(R4&lt;$U$3,"negativno",LOOKUP(R4,$U$3:$U$7,$V$3:$V$7)))</f>
+        <f t="shared" si="3"/>
         <v>7</v>
       </c>
       <c r="U4" s="2">
@@ -6184,11 +6180,11 @@
       <c r="V4" s="3">
         <v>7</v>
       </c>
-      <c r="X4" s="19" t="s">
+      <c r="X4" s="20" t="s">
         <v>116</v>
       </c>
-      <c r="Y4" s="20"/>
-      <c r="Z4" s="21">
+      <c r="Y4" s="21"/>
+      <c r="Z4" s="17">
         <f>AVERAGE(Q3:Q117)</f>
         <v>43.005050505050505</v>
       </c>
@@ -6238,19 +6234,19 @@
       </c>
       <c r="O5" s="3"/>
       <c r="P5" s="7">
-        <f>IF(COUNTBLANK(D5:M5)=10,"",SUM(D5:M5))</f>
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="Q5" s="7">
-        <f>IF(COUNTBLANK(D5:O5)=12,"",MAX(N5+P5,O5+0.5*P5))</f>
+        <f t="shared" si="1"/>
         <v>120</v>
       </c>
       <c r="R5" s="8">
-        <f>IF(COUNTBLANK(N5:O5)=2,"",IF(AND(SUM(N5:O5)=0,P5&lt;0),0,Q5/100))</f>
+        <f t="shared" si="2"/>
         <v>1.2</v>
       </c>
       <c r="S5" s="7">
-        <f>IF(R5="","ni opravljal izpita",IF(R5&lt;$U$3,"negativno",LOOKUP(R5,$U$3:$U$7,$V$3:$V$7)))</f>
+        <f t="shared" si="3"/>
         <v>10</v>
       </c>
       <c r="U5" s="2">
@@ -6259,10 +6255,10 @@
       <c r="V5" s="3">
         <v>8</v>
       </c>
-      <c r="X5" s="19" t="s">
+      <c r="X5" s="20" t="s">
         <v>120</v>
       </c>
-      <c r="Y5" s="20"/>
+      <c r="Y5" s="21"/>
       <c r="Z5" s="3">
         <f>MODE(Q3:Q117)</f>
         <v>58</v>
@@ -6291,19 +6287,19 @@
       <c r="N6" s="3"/>
       <c r="O6" s="3"/>
       <c r="P6" s="7" t="str">
-        <f>IF(COUNTBLANK(D6:M6)=10,"",SUM(D6:M6))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="Q6" s="7" t="str">
-        <f>IF(COUNTBLANK(D6:O6)=12,"",MAX(N6+P6,O6+0.5*P6))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="R6" s="8" t="str">
-        <f>IF(COUNTBLANK(N6:O6)=2,"",IF(AND(SUM(N6:O6)=0,P6&lt;0),0,Q6/100))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="S6" s="7" t="str">
-        <f>IF(R6="","ni opravljal izpita",IF(R6&lt;$U$3,"negativno",LOOKUP(R6,$U$3:$U$7,$V$3:$V$7)))</f>
+        <f t="shared" si="3"/>
         <v>ni opravljal izpita</v>
       </c>
       <c r="U6" s="2">
@@ -6312,10 +6308,10 @@
       <c r="V6" s="3">
         <v>9</v>
       </c>
-      <c r="X6" s="19" t="s">
+      <c r="X6" s="20" t="s">
         <v>124</v>
       </c>
-      <c r="Y6" s="20"/>
+      <c r="Y6" s="21"/>
       <c r="Z6" s="3">
         <f>MEDIAN(Q3:Q117)</f>
         <v>45</v>
@@ -6356,19 +6352,19 @@
         <v>60</v>
       </c>
       <c r="P7" s="7">
-        <f>IF(COUNTBLANK(D7:M7)=10,"",SUM(D7:M7))</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="Q7" s="7">
-        <f>IF(COUNTBLANK(D7:O7)=12,"",MAX(N7+P7,O7+0.5*P7))</f>
+        <f t="shared" si="1"/>
         <v>61.5</v>
       </c>
       <c r="R7" s="8">
-        <f>IF(COUNTBLANK(N7:O7)=2,"",IF(AND(SUM(N7:O7)=0,P7&lt;0),0,Q7/100))</f>
+        <f t="shared" si="2"/>
         <v>0.61499999999999999</v>
       </c>
       <c r="S7" s="7">
-        <f>IF(R7="","ni opravljal izpita",IF(R7&lt;$U$3,"negativno",LOOKUP(R7,$U$3:$U$7,$V$3:$V$7)))</f>
+        <f t="shared" si="3"/>
         <v>7</v>
       </c>
       <c r="U7" s="2">
@@ -6377,10 +6373,10 @@
       <c r="V7" s="3">
         <v>10</v>
       </c>
-      <c r="X7" s="19" t="s">
+      <c r="X7" s="20" t="s">
         <v>121</v>
       </c>
-      <c r="Y7" s="20"/>
+      <c r="Y7" s="21"/>
       <c r="Z7" s="3">
         <f>MAX(Q3:Q117)</f>
         <v>120</v>
@@ -6429,25 +6425,25 @@
       <c r="N8" s="3"/>
       <c r="O8" s="3"/>
       <c r="P8" s="7">
-        <f>IF(COUNTBLANK(D8:M8)=10,"",SUM(D8:M8))</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="Q8" s="7">
-        <f>IF(COUNTBLANK(D8:O8)=12,"",MAX(N8+P8,O8+0.5*P8))</f>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="R8" s="8" t="str">
-        <f>IF(COUNTBLANK(N8:O8)=2,"",IF(AND(SUM(N8:O8)=0,P8&lt;0),0,Q8/100))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="S8" s="7" t="str">
-        <f>IF(R8="","ni opravljal izpita",IF(R8&lt;$U$3,"negativno",LOOKUP(R8,$U$3:$U$7,$V$3:$V$7)))</f>
+        <f t="shared" si="3"/>
         <v>ni opravljal izpita</v>
       </c>
-      <c r="X8" s="19" t="s">
+      <c r="X8" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="Y8" s="20"/>
+      <c r="Y8" s="21"/>
       <c r="Z8" s="3">
         <f>MIN(Q3:Q117)</f>
         <v>0</v>
@@ -6492,19 +6488,19 @@
       </c>
       <c r="O9" s="3"/>
       <c r="P9" s="7">
-        <f>IF(COUNTBLANK(D9:M9)=10,"",SUM(D9:M9))</f>
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="Q9" s="7">
-        <f>IF(COUNTBLANK(D9:O9)=12,"",MAX(N9+P9,O9+0.5*P9))</f>
+        <f t="shared" si="1"/>
         <v>58</v>
       </c>
       <c r="R9" s="8">
-        <f>IF(COUNTBLANK(N9:O9)=2,"",IF(AND(SUM(N9:O9)=0,P9&lt;0),0,Q9/100))</f>
+        <f t="shared" si="2"/>
         <v>0.57999999999999996</v>
       </c>
       <c r="S9" s="7">
-        <f>IF(R9="","ni opravljal izpita",IF(R9&lt;$U$3,"negativno",LOOKUP(R9,$U$3:$U$7,$V$3:$V$7)))</f>
+        <f t="shared" si="3"/>
         <v>6</v>
       </c>
     </row>
@@ -6534,15 +6530,15 @@
       </c>
       <c r="P10" s="7"/>
       <c r="Q10" s="7">
-        <f>IF(COUNTBLANK(D10:O10)=12,"",MAX(N10+P10,O10+0.5*P10))</f>
+        <f t="shared" si="1"/>
         <v>20</v>
       </c>
       <c r="R10" s="8">
-        <f>IF(COUNTBLANK(N10:O10)=2,"",IF(AND(SUM(N10:O10)=0,P10&lt;0),0,Q10/100))</f>
+        <f t="shared" si="2"/>
         <v>0.2</v>
       </c>
       <c r="S10" s="7" t="str">
-        <f>IF(R10="","ni opravljal izpita",IF(R10&lt;$U$3,"negativno",LOOKUP(R10,$U$3:$U$7,$V$3:$V$7)))</f>
+        <f t="shared" si="3"/>
         <v>negativno</v>
       </c>
       <c r="W10" s="10" t="s">
@@ -6604,19 +6600,19 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="7">
-        <f>IF(COUNTBLANK(D11:M11)=10,"",SUM(D11:M11))</f>
+        <f t="shared" ref="P11:P42" si="4">IF(COUNTBLANK(D11:M11)=10,"",SUM(D11:M11))</f>
         <v>9</v>
       </c>
       <c r="Q11" s="7">
-        <f>IF(COUNTBLANK(D11:O11)=12,"",MAX(N11+P11,O11+0.5*P11))</f>
+        <f t="shared" si="1"/>
         <v>9</v>
       </c>
       <c r="R11" s="8" t="str">
-        <f>IF(COUNTBLANK(N11:O11)=2,"",IF(AND(SUM(N11:O11)=0,P11&lt;0),0,Q11/100))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="S11" s="7" t="str">
-        <f>IF(R11="","ni opravljal izpita",IF(R11&lt;$U$3,"negativno",LOOKUP(R11,$U$3:$U$7,$V$3:$V$7)))</f>
+        <f t="shared" si="3"/>
         <v>ni opravljal izpita</v>
       </c>
       <c r="W11" s="5">
@@ -6687,19 +6683,19 @@
       <c r="N12" s="3"/>
       <c r="O12" s="3"/>
       <c r="P12" s="7">
-        <f>IF(COUNTBLANK(D12:M12)=10,"",SUM(D12:M12))</f>
+        <f t="shared" si="4"/>
         <v>13</v>
       </c>
       <c r="Q12" s="7">
-        <f>IF(COUNTBLANK(D12:O12)=12,"",MAX(N12+P12,O12+0.5*P12))</f>
+        <f t="shared" si="1"/>
         <v>13</v>
       </c>
       <c r="R12" s="8" t="str">
-        <f>IF(COUNTBLANK(N12:O12)=2,"",IF(AND(SUM(N12:O12)=0,P12&lt;0),0,Q12/100))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="S12" s="7" t="str">
-        <f>IF(R12="","ni opravljal izpita",IF(R12&lt;$U$3,"negativno",LOOKUP(R12,$U$3:$U$7,$V$3:$V$7)))</f>
+        <f t="shared" si="3"/>
         <v>ni opravljal izpita</v>
       </c>
       <c r="W12" s="5">
@@ -6709,11 +6705,11 @@
         <v>6</v>
       </c>
       <c r="Y12" s="3">
-        <f t="shared" ref="Y12:Y17" si="0">COUNTIF($S$3:$S$117,X12)</f>
+        <f t="shared" ref="Y12:Y17" si="5">COUNTIF($S$3:$S$117,X12)</f>
         <v>13</v>
       </c>
       <c r="Z12" s="2">
-        <f t="shared" ref="Z12:Z17" si="1">Y12/$Y$18</f>
+        <f t="shared" ref="Z12:Z17" si="6">Y12/$Y$18</f>
         <v>0.11304347826086956</v>
       </c>
       <c r="AA12" s="3">
@@ -6721,11 +6717,11 @@
         <v>48</v>
       </c>
       <c r="AB12" s="2">
-        <f t="shared" ref="AB12:AB17" si="2">AA12/$Y$18</f>
+        <f t="shared" ref="AB12:AB17" si="7">AA12/$Y$18</f>
         <v>0.41739130434782606</v>
       </c>
       <c r="AC12" s="16">
-        <f t="shared" ref="AC12:AC17" si="3">Z12*360</f>
+        <f t="shared" ref="AC12:AC17" si="8">Z12*360</f>
         <v>40.695652173913047</v>
       </c>
     </row>
@@ -6774,19 +6770,19 @@
       </c>
       <c r="O13" s="3"/>
       <c r="P13" s="7">
-        <f>IF(COUNTBLANK(D13:M13)=10,"",SUM(D13:M13))</f>
+        <f t="shared" si="4"/>
         <v>16</v>
       </c>
       <c r="Q13" s="7">
-        <f>IF(COUNTBLANK(D13:O13)=12,"",MAX(N13+P13,O13+0.5*P13))</f>
+        <f t="shared" si="1"/>
         <v>31</v>
       </c>
       <c r="R13" s="8">
-        <f>IF(COUNTBLANK(N13:O13)=2,"",IF(AND(SUM(N13:O13)=0,P13&lt;0),0,Q13/100))</f>
+        <f t="shared" si="2"/>
         <v>0.31</v>
       </c>
       <c r="S13" s="7" t="str">
-        <f>IF(R13="","ni opravljal izpita",IF(R13&lt;$U$3,"negativno",LOOKUP(R13,$U$3:$U$7,$V$3:$V$7)))</f>
+        <f t="shared" si="3"/>
         <v>negativno</v>
       </c>
       <c r="W13" s="5">
@@ -6796,23 +6792,23 @@
         <v>7</v>
       </c>
       <c r="Y13" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>15</v>
       </c>
       <c r="Z13" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>0.13043478260869565</v>
       </c>
       <c r="AA13" s="3">
-        <f t="shared" ref="AA13:AA17" si="4">AA12+Y13</f>
+        <f t="shared" ref="AA13:AA17" si="9">AA12+Y13</f>
         <v>63</v>
       </c>
       <c r="AB13" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="7"/>
         <v>0.54782608695652169</v>
       </c>
       <c r="AC13" s="16">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v>46.95652173913043</v>
       </c>
     </row>
@@ -6857,19 +6853,19 @@
         <v>13</v>
       </c>
       <c r="P14" s="7">
-        <f>IF(COUNTBLANK(D14:M14)=10,"",SUM(D14:M14))</f>
+        <f t="shared" si="4"/>
         <v>13</v>
       </c>
       <c r="Q14" s="7">
-        <f>IF(COUNTBLANK(D14:O14)=12,"",MAX(N14+P14,O14+0.5*P14))</f>
+        <f t="shared" si="1"/>
         <v>19.5</v>
       </c>
       <c r="R14" s="8">
-        <f>IF(COUNTBLANK(N14:O14)=2,"",IF(AND(SUM(N14:O14)=0,P14&lt;0),0,Q14/100))</f>
+        <f t="shared" si="2"/>
         <v>0.19500000000000001</v>
       </c>
       <c r="S14" s="7" t="str">
-        <f>IF(R14="","ni opravljal izpita",IF(R14&lt;$U$3,"negativno",LOOKUP(R14,$U$3:$U$7,$V$3:$V$7)))</f>
+        <f t="shared" si="3"/>
         <v>negativno</v>
       </c>
       <c r="W14" s="5">
@@ -6879,23 +6875,23 @@
         <v>8</v>
       </c>
       <c r="Y14" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>8</v>
       </c>
       <c r="Z14" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>6.9565217391304349E-2</v>
       </c>
       <c r="AA14" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>71</v>
       </c>
       <c r="AB14" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="7"/>
         <v>0.61739130434782608</v>
       </c>
       <c r="AC14" s="16">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v>25.043478260869566</v>
       </c>
     </row>
@@ -6944,19 +6940,19 @@
       </c>
       <c r="O15" s="3"/>
       <c r="P15" s="7">
-        <f>IF(COUNTBLANK(D15:M15)=10,"",SUM(D15:M15))</f>
+        <f t="shared" si="4"/>
         <v>18</v>
       </c>
       <c r="Q15" s="7">
-        <f>IF(COUNTBLANK(D15:O15)=12,"",MAX(N15+P15,O15+0.5*P15))</f>
+        <f t="shared" si="1"/>
         <v>82</v>
       </c>
       <c r="R15" s="8">
-        <f>IF(COUNTBLANK(N15:O15)=2,"",IF(AND(SUM(N15:O15)=0,P15&lt;0),0,Q15/100))</f>
+        <f t="shared" si="2"/>
         <v>0.82</v>
       </c>
       <c r="S15" s="7">
-        <f>IF(R15="","ni opravljal izpita",IF(R15&lt;$U$3,"negativno",LOOKUP(R15,$U$3:$U$7,$V$3:$V$7)))</f>
+        <f t="shared" si="3"/>
         <v>9</v>
       </c>
       <c r="W15" s="5">
@@ -6966,23 +6962,23 @@
         <v>9</v>
       </c>
       <c r="Y15" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>6</v>
       </c>
       <c r="Z15" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>5.2173913043478258E-2</v>
       </c>
       <c r="AA15" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>77</v>
       </c>
       <c r="AB15" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="7"/>
         <v>0.66956521739130437</v>
       </c>
       <c r="AC15" s="16">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v>18.782608695652172</v>
       </c>
     </row>
@@ -7029,19 +7025,19 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="7">
-        <f>IF(COUNTBLANK(D16:M16)=10,"",SUM(D16:M16))</f>
+        <f t="shared" si="4"/>
         <v>16</v>
       </c>
       <c r="Q16" s="7">
-        <f>IF(COUNTBLANK(D16:O16)=12,"",MAX(N16+P16,O16+0.5*P16))</f>
+        <f t="shared" si="1"/>
         <v>16</v>
       </c>
       <c r="R16" s="8" t="str">
-        <f>IF(COUNTBLANK(N16:O16)=2,"",IF(AND(SUM(N16:O16)=0,P16&lt;0),0,Q16/100))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="S16" s="7" t="str">
-        <f>IF(R16="","ni opravljal izpita",IF(R16&lt;$U$3,"negativno",LOOKUP(R16,$U$3:$U$7,$V$3:$V$7)))</f>
+        <f t="shared" si="3"/>
         <v>ni opravljal izpita</v>
       </c>
       <c r="W16" s="5">
@@ -7051,23 +7047,23 @@
         <v>10</v>
       </c>
       <c r="Y16" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>4</v>
       </c>
       <c r="Z16" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>3.4782608695652174E-2</v>
       </c>
       <c r="AA16" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>81</v>
       </c>
       <c r="AB16" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="7"/>
         <v>0.70434782608695656</v>
       </c>
       <c r="AC16" s="16">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v>12.521739130434783</v>
       </c>
     </row>
@@ -7110,19 +7106,19 @@
       </c>
       <c r="O17" s="3"/>
       <c r="P17" s="7">
-        <f>IF(COUNTBLANK(D17:M17)=10,"",SUM(D17:M17))</f>
+        <f t="shared" si="4"/>
         <v>8</v>
       </c>
       <c r="Q17" s="7">
-        <f>IF(COUNTBLANK(D17:O17)=12,"",MAX(N17+P17,O17+0.5*P17))</f>
+        <f t="shared" si="1"/>
         <v>55</v>
       </c>
       <c r="R17" s="8">
-        <f>IF(COUNTBLANK(N17:O17)=2,"",IF(AND(SUM(N17:O17)=0,P17&lt;0),0,Q17/100))</f>
+        <f t="shared" si="2"/>
         <v>0.55000000000000004</v>
       </c>
       <c r="S17" s="7">
-        <f>IF(R17="","ni opravljal izpita",IF(R17&lt;$U$3,"negativno",LOOKUP(R17,$U$3:$U$7,$V$3:$V$7)))</f>
+        <f t="shared" si="3"/>
         <v>6</v>
       </c>
       <c r="W17" s="5">
@@ -7132,23 +7128,23 @@
         <v>111</v>
       </c>
       <c r="Y17" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>34</v>
       </c>
       <c r="Z17" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>0.29565217391304349</v>
       </c>
       <c r="AA17" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>115</v>
       </c>
       <c r="AB17" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="AC17" s="16">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v>106.43478260869566</v>
       </c>
     </row>
@@ -7183,19 +7179,19 @@
       <c r="N18" s="3"/>
       <c r="O18" s="3"/>
       <c r="P18" s="7">
-        <f>IF(COUNTBLANK(D18:M18)=10,"",SUM(D18:M18))</f>
+        <f t="shared" si="4"/>
         <v>3</v>
       </c>
       <c r="Q18" s="7">
-        <f>IF(COUNTBLANK(D18:O18)=12,"",MAX(N18+P18,O18+0.5*P18))</f>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="R18" s="8" t="str">
-        <f>IF(COUNTBLANK(N18:O18)=2,"",IF(AND(SUM(N18:O18)=0,P18&lt;0),0,Q18/100))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="S18" s="7" t="str">
-        <f>IF(R18="","ni opravljal izpita",IF(R18&lt;$U$3,"negativno",LOOKUP(R18,$U$3:$U$7,$V$3:$V$7)))</f>
+        <f t="shared" si="3"/>
         <v>ni opravljal izpita</v>
       </c>
       <c r="X18" s="10" t="s">
@@ -7206,7 +7202,7 @@
         <v>115</v>
       </c>
       <c r="Z18" s="13">
-        <f t="shared" ref="Z18" si="5">SUM(Z11:Z17)</f>
+        <f t="shared" ref="Z18" si="10">SUM(Z11:Z17)</f>
         <v>1.0000000000000002</v>
       </c>
       <c r="AA18" s="15"/>
@@ -7249,19 +7245,19 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="7">
-        <f>IF(COUNTBLANK(D19:M19)=10,"",SUM(D19:M19))</f>
+        <f t="shared" si="4"/>
         <v>3</v>
       </c>
       <c r="Q19" s="7">
-        <f>IF(COUNTBLANK(D19:O19)=12,"",MAX(N19+P19,O19+0.5*P19))</f>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="R19" s="8" t="str">
-        <f>IF(COUNTBLANK(N19:O19)=2,"",IF(AND(SUM(N19:O19)=0,P19&lt;0),0,Q19/100))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="S19" s="7" t="str">
-        <f>IF(R19="","ni opravljal izpita",IF(R19&lt;$U$3,"negativno",LOOKUP(R19,$U$3:$U$7,$V$3:$V$7)))</f>
+        <f t="shared" si="3"/>
         <v>ni opravljal izpita</v>
       </c>
       <c r="U19" s="1"/>
@@ -7301,19 +7297,19 @@
         <v>31</v>
       </c>
       <c r="P20" s="7">
-        <f>IF(COUNTBLANK(D20:M20)=10,"",SUM(D20:M20))</f>
+        <f t="shared" si="4"/>
         <v>6</v>
       </c>
       <c r="Q20" s="7">
-        <f>IF(COUNTBLANK(D20:O20)=12,"",MAX(N20+P20,O20+0.5*P20))</f>
+        <f t="shared" si="1"/>
         <v>45</v>
       </c>
       <c r="R20" s="8">
-        <f>IF(COUNTBLANK(N20:O20)=2,"",IF(AND(SUM(N20:O20)=0,P20&lt;0),0,Q20/100))</f>
+        <f t="shared" si="2"/>
         <v>0.45</v>
       </c>
       <c r="S20" s="7" t="str">
-        <f>IF(R20="","ni opravljal izpita",IF(R20&lt;$U$3,"negativno",LOOKUP(R20,$U$3:$U$7,$V$3:$V$7)))</f>
+        <f t="shared" si="3"/>
         <v>negativno</v>
       </c>
       <c r="U20" s="1"/>
@@ -7356,19 +7352,19 @@
       </c>
       <c r="O21" s="3"/>
       <c r="P21" s="7">
-        <f>IF(COUNTBLANK(D21:M21)=10,"",SUM(D21:M21))</f>
+        <f t="shared" si="4"/>
         <v>2</v>
       </c>
       <c r="Q21" s="7">
-        <f>IF(COUNTBLANK(D21:O21)=12,"",MAX(N21+P21,O21+0.5*P21))</f>
+        <f t="shared" si="1"/>
         <v>7</v>
       </c>
       <c r="R21" s="8">
-        <f>IF(COUNTBLANK(N21:O21)=2,"",IF(AND(SUM(N21:O21)=0,P21&lt;0),0,Q21/100))</f>
+        <f t="shared" si="2"/>
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="S21" s="7" t="str">
-        <f>IF(R21="","ni opravljal izpita",IF(R21&lt;$U$3,"negativno",LOOKUP(R21,$U$3:$U$7,$V$3:$V$7)))</f>
+        <f t="shared" si="3"/>
         <v>negativno</v>
       </c>
       <c r="U21" s="1"/>
@@ -7425,19 +7421,19 @@
       </c>
       <c r="O22" s="3"/>
       <c r="P22" s="7">
-        <f>IF(COUNTBLANK(D22:M22)=10,"",SUM(D22:M22))</f>
+        <f t="shared" si="4"/>
         <v>16</v>
       </c>
       <c r="Q22" s="7">
-        <f>IF(COUNTBLANK(D22:O22)=12,"",MAX(N22+P22,O22+0.5*P22))</f>
+        <f t="shared" si="1"/>
         <v>69</v>
       </c>
       <c r="R22" s="8">
-        <f>IF(COUNTBLANK(N22:O22)=2,"",IF(AND(SUM(N22:O22)=0,P22&lt;0),0,Q22/100))</f>
+        <f t="shared" si="2"/>
         <v>0.69</v>
       </c>
       <c r="S22" s="7">
-        <f>IF(R22="","ni opravljal izpita",IF(R22&lt;$U$3,"negativno",LOOKUP(R22,$U$3:$U$7,$V$3:$V$7)))</f>
+        <f t="shared" si="3"/>
         <v>7</v>
       </c>
       <c r="U22" s="1"/>
@@ -7483,30 +7479,30 @@
       </c>
       <c r="O23" s="3"/>
       <c r="P23" s="7">
-        <f>IF(COUNTBLANK(D23:M23)=10,"",SUM(D23:M23))</f>
+        <f t="shared" si="4"/>
         <v>12</v>
       </c>
       <c r="Q23" s="7">
-        <f>IF(COUNTBLANK(D23:O23)=12,"",MAX(N23+P23,O23+0.5*P23))</f>
+        <f t="shared" si="1"/>
         <v>67</v>
       </c>
       <c r="R23" s="8">
-        <f>IF(COUNTBLANK(N23:O23)=2,"",IF(AND(SUM(N23:O23)=0,P23&lt;0),0,Q23/100))</f>
+        <f t="shared" si="2"/>
         <v>0.67</v>
       </c>
       <c r="S23" s="7">
-        <f>IF(R23="","ni opravljal izpita",IF(R23&lt;$U$3,"negativno",LOOKUP(R23,$U$3:$U$7,$V$3:$V$7)))</f>
+        <f t="shared" si="3"/>
         <v>7</v>
       </c>
-      <c r="W23" s="17" t="s">
+      <c r="W23" s="18" t="s">
         <v>131</v>
       </c>
-      <c r="X23" s="17"/>
-      <c r="Y23" s="17"/>
-      <c r="Z23" s="17"/>
-      <c r="AA23" s="17"/>
-      <c r="AB23" s="17"/>
-      <c r="AC23" s="17"/>
+      <c r="X23" s="18"/>
+      <c r="Y23" s="18"/>
+      <c r="Z23" s="18"/>
+      <c r="AA23" s="18"/>
+      <c r="AB23" s="18"/>
+      <c r="AC23" s="18"/>
     </row>
     <row r="24" spans="1:29" ht="18" x14ac:dyDescent="0.35">
       <c r="A24" s="5">
@@ -7535,19 +7531,19 @@
       </c>
       <c r="O24" s="3"/>
       <c r="P24" s="7">
-        <f>IF(COUNTBLANK(D24:M24)=10,"",SUM(D24:M24))</f>
+        <f t="shared" si="4"/>
         <v>2</v>
       </c>
       <c r="Q24" s="7">
-        <f>IF(COUNTBLANK(D24:O24)=12,"",MAX(N24+P24,O24+0.5*P24))</f>
+        <f t="shared" si="1"/>
         <v>32</v>
       </c>
       <c r="R24" s="8">
-        <f>IF(COUNTBLANK(N24:O24)=2,"",IF(AND(SUM(N24:O24)=0,P24&lt;0),0,Q24/100))</f>
+        <f t="shared" si="2"/>
         <v>0.32</v>
       </c>
       <c r="S24" s="7" t="str">
-        <f>IF(R24="","ni opravljal izpita",IF(R24&lt;$U$3,"negativno",LOOKUP(R24,$U$3:$U$7,$V$3:$V$7)))</f>
+        <f t="shared" si="3"/>
         <v>negativno</v>
       </c>
       <c r="W24" s="10" t="s">
@@ -7617,19 +7613,19 @@
       </c>
       <c r="O25" s="3"/>
       <c r="P25" s="7">
-        <f>IF(COUNTBLANK(D25:M25)=10,"",SUM(D25:M25))</f>
+        <f t="shared" si="4"/>
         <v>17</v>
       </c>
       <c r="Q25" s="7">
-        <f>IF(COUNTBLANK(D25:O25)=12,"",MAX(N25+P25,O25+0.5*P25))</f>
+        <f t="shared" si="1"/>
         <v>67</v>
       </c>
       <c r="R25" s="8">
-        <f>IF(COUNTBLANK(N25:O25)=2,"",IF(AND(SUM(N25:O25)=0,P25&lt;0),0,Q25/100))</f>
+        <f t="shared" si="2"/>
         <v>0.67</v>
       </c>
       <c r="S25" s="7">
-        <f>IF(R25="","ni opravljal izpita",IF(R25&lt;$U$3,"negativno",LOOKUP(R25,$U$3:$U$7,$V$3:$V$7)))</f>
+        <f t="shared" si="3"/>
         <v>7</v>
       </c>
       <c r="W25" s="5">
@@ -7680,19 +7676,19 @@
       <c r="N26" s="3"/>
       <c r="O26" s="3"/>
       <c r="P26" s="7" t="str">
-        <f>IF(COUNTBLANK(D26:M26)=10,"",SUM(D26:M26))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="Q26" s="7" t="str">
-        <f>IF(COUNTBLANK(D26:O26)=12,"",MAX(N26+P26,O26+0.5*P26))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="R26" s="8" t="str">
-        <f>IF(COUNTBLANK(N26:O26)=2,"",IF(AND(SUM(N26:O26)=0,P26&lt;0),0,Q26/100))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="S26" s="7" t="str">
-        <f>IF(R26="","ni opravljal izpita",IF(R26&lt;$U$3,"negativno",LOOKUP(R26,$U$3:$U$7,$V$3:$V$7)))</f>
+        <f t="shared" si="3"/>
         <v>ni opravljal izpita</v>
       </c>
       <c r="W26" s="5">
@@ -7705,11 +7701,11 @@
         <v>62</v>
       </c>
       <c r="Z26" s="3">
-        <f t="shared" ref="Z26:Z29" si="6">Y26-X26</f>
+        <f t="shared" ref="Z26:Z29" si="11">Y26-X26</f>
         <v>12</v>
       </c>
       <c r="AA26" s="3">
-        <f t="shared" ref="AA26:AA29" si="7">(Y26+X26)/2</f>
+        <f t="shared" ref="AA26:AA29" si="12">(Y26+X26)/2</f>
         <v>56</v>
       </c>
       <c r="AB26" s="3">
@@ -7760,19 +7756,19 @@
       </c>
       <c r="O27" s="3"/>
       <c r="P27" s="7">
-        <f>IF(COUNTBLANK(D27:M27)=10,"",SUM(D27:M27))</f>
+        <f t="shared" si="4"/>
         <v>7</v>
       </c>
       <c r="Q27" s="7">
-        <f>IF(COUNTBLANK(D27:O27)=12,"",MAX(N27+P27,O27+0.5*P27))</f>
+        <f t="shared" si="1"/>
         <v>38</v>
       </c>
       <c r="R27" s="8">
-        <f>IF(COUNTBLANK(N27:O27)=2,"",IF(AND(SUM(N27:O27)=0,P27&lt;0),0,Q27/100))</f>
+        <f t="shared" si="2"/>
         <v>0.38</v>
       </c>
       <c r="S27" s="7" t="str">
-        <f>IF(R27="","ni opravljal izpita",IF(R27&lt;$U$3,"negativno",LOOKUP(R27,$U$3:$U$7,$V$3:$V$7)))</f>
+        <f t="shared" si="3"/>
         <v>negativno</v>
       </c>
       <c r="W27" s="5">
@@ -7785,11 +7781,11 @@
         <v>76</v>
       </c>
       <c r="Z27" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>14</v>
       </c>
       <c r="AA27" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>69</v>
       </c>
       <c r="AB27" s="3">
@@ -7822,19 +7818,19 @@
       <c r="N28" s="3"/>
       <c r="O28" s="3"/>
       <c r="P28" s="7" t="str">
-        <f>IF(COUNTBLANK(D28:M28)=10,"",SUM(D28:M28))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="Q28" s="7" t="str">
-        <f>IF(COUNTBLANK(D28:O28)=12,"",MAX(N28+P28,O28+0.5*P28))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="R28" s="8" t="str">
-        <f>IF(COUNTBLANK(N28:O28)=2,"",IF(AND(SUM(N28:O28)=0,P28&lt;0),0,Q28/100))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="S28" s="7" t="str">
-        <f>IF(R28="","ni opravljal izpita",IF(R28&lt;$U$3,"negativno",LOOKUP(R28,$U$3:$U$7,$V$3:$V$7)))</f>
+        <f t="shared" si="3"/>
         <v>ni opravljal izpita</v>
       </c>
       <c r="W28" s="5">
@@ -7847,11 +7843,11 @@
         <v>88</v>
       </c>
       <c r="Z28" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>12</v>
       </c>
       <c r="AA28" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>82</v>
       </c>
       <c r="AB28" s="3">
@@ -7904,19 +7900,19 @@
       </c>
       <c r="O29" s="3"/>
       <c r="P29" s="7">
-        <f>IF(COUNTBLANK(D29:M29)=10,"",SUM(D29:M29))</f>
+        <f t="shared" si="4"/>
         <v>13</v>
       </c>
       <c r="Q29" s="7">
-        <f>IF(COUNTBLANK(D29:O29)=12,"",MAX(N29+P29,O29+0.5*P29))</f>
+        <f t="shared" si="1"/>
         <v>51</v>
       </c>
       <c r="R29" s="8">
-        <f>IF(COUNTBLANK(N29:O29)=2,"",IF(AND(SUM(N29:O29)=0,P29&lt;0),0,Q29/100))</f>
+        <f t="shared" si="2"/>
         <v>0.51</v>
       </c>
       <c r="S29" s="7">
-        <f>IF(R29="","ni opravljal izpita",IF(R29&lt;$U$3,"negativno",LOOKUP(R29,$U$3:$U$7,$V$3:$V$7)))</f>
+        <f t="shared" si="3"/>
         <v>6</v>
       </c>
       <c r="W29" s="5">
@@ -7929,11 +7925,11 @@
         <v>100</v>
       </c>
       <c r="Z29" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>12</v>
       </c>
       <c r="AA29" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>94</v>
       </c>
       <c r="AB29" s="3">
@@ -7982,19 +7978,19 @@
         <v>33</v>
       </c>
       <c r="P30" s="7">
-        <f>IF(COUNTBLANK(D30:M30)=10,"",SUM(D30:M30))</f>
+        <f t="shared" si="4"/>
         <v>5</v>
       </c>
       <c r="Q30" s="7">
-        <f>IF(COUNTBLANK(D30:O30)=12,"",MAX(N30+P30,O30+0.5*P30))</f>
+        <f t="shared" si="1"/>
         <v>35.5</v>
       </c>
       <c r="R30" s="8">
-        <f>IF(COUNTBLANK(N30:O30)=2,"",IF(AND(SUM(N30:O30)=0,P30&lt;0),0,Q30/100))</f>
+        <f t="shared" si="2"/>
         <v>0.35499999999999998</v>
       </c>
       <c r="S30" s="7" t="str">
-        <f>IF(R30="","ni opravljal izpita",IF(R30&lt;$U$3,"negativno",LOOKUP(R30,$U$3:$U$7,$V$3:$V$7)))</f>
+        <f t="shared" si="3"/>
         <v>negativno</v>
       </c>
       <c r="AA30" s="10" t="s">
@@ -8048,19 +8044,19 @@
         <v>30</v>
       </c>
       <c r="P31" s="7">
-        <f>IF(COUNTBLANK(D31:M31)=10,"",SUM(D31:M31))</f>
+        <f t="shared" si="4"/>
         <v>12</v>
       </c>
       <c r="Q31" s="7">
-        <f>IF(COUNTBLANK(D31:O31)=12,"",MAX(N31+P31,O31+0.5*P31))</f>
+        <f t="shared" si="1"/>
         <v>37</v>
       </c>
       <c r="R31" s="8">
-        <f>IF(COUNTBLANK(N31:O31)=2,"",IF(AND(SUM(N31:O31)=0,P31&lt;0),0,Q31/100))</f>
+        <f t="shared" si="2"/>
         <v>0.37</v>
       </c>
       <c r="S31" s="7" t="str">
-        <f>IF(R31="","ni opravljal izpita",IF(R31&lt;$U$3,"negativno",LOOKUP(R31,$U$3:$U$7,$V$3:$V$7)))</f>
+        <f t="shared" si="3"/>
         <v>negativno</v>
       </c>
       <c r="W31" s="10" t="s">
@@ -8110,19 +8106,19 @@
       </c>
       <c r="O32" s="3"/>
       <c r="P32" s="7">
-        <f>IF(COUNTBLANK(D32:M32)=10,"",SUM(D32:M32))</f>
+        <f t="shared" si="4"/>
         <v>14</v>
       </c>
       <c r="Q32" s="7">
-        <f>IF(COUNTBLANK(D32:O32)=12,"",MAX(N32+P32,O32+0.5*P32))</f>
+        <f t="shared" si="1"/>
         <v>82</v>
       </c>
       <c r="R32" s="8">
-        <f>IF(COUNTBLANK(N32:O32)=2,"",IF(AND(SUM(N32:O32)=0,P32&lt;0),0,Q32/100))</f>
+        <f t="shared" si="2"/>
         <v>0.82</v>
       </c>
       <c r="S32" s="7">
-        <f>IF(R32="","ni opravljal izpita",IF(R32&lt;$U$3,"negativno",LOOKUP(R32,$U$3:$U$7,$V$3:$V$7)))</f>
+        <f t="shared" si="3"/>
         <v>9</v>
       </c>
       <c r="W32" s="5" t="s">
@@ -8178,19 +8174,19 @@
       </c>
       <c r="O33" s="3"/>
       <c r="P33" s="7">
-        <f>IF(COUNTBLANK(D33:M33)=10,"",SUM(D33:M33))</f>
+        <f t="shared" si="4"/>
         <v>11</v>
       </c>
       <c r="Q33" s="7">
-        <f>IF(COUNTBLANK(D33:O33)=12,"",MAX(N33+P33,O33+0.5*P33))</f>
+        <f t="shared" si="1"/>
         <v>86</v>
       </c>
       <c r="R33" s="8">
-        <f>IF(COUNTBLANK(N33:O33)=2,"",IF(AND(SUM(N33:O33)=0,P33&lt;0),0,Q33/100))</f>
+        <f t="shared" si="2"/>
         <v>0.86</v>
       </c>
       <c r="S33" s="7">
-        <f>IF(R33="","ni opravljal izpita",IF(R33&lt;$U$3,"negativno",LOOKUP(R33,$U$3:$U$7,$V$3:$V$7)))</f>
+        <f t="shared" si="3"/>
         <v>9</v>
       </c>
       <c r="W33" s="5" t="s">
@@ -8246,19 +8242,19 @@
       </c>
       <c r="O34" s="3"/>
       <c r="P34" s="7">
-        <f>IF(COUNTBLANK(D34:M34)=10,"",SUM(D34:M34))</f>
+        <f t="shared" si="4"/>
         <v>8</v>
       </c>
       <c r="Q34" s="7">
-        <f>IF(COUNTBLANK(D34:O34)=12,"",MAX(N34+P34,O34+0.5*P34))</f>
+        <f t="shared" si="1"/>
         <v>45</v>
       </c>
       <c r="R34" s="8">
-        <f>IF(COUNTBLANK(N34:O34)=2,"",IF(AND(SUM(N34:O34)=0,P34&lt;0),0,Q34/100))</f>
+        <f t="shared" si="2"/>
         <v>0.45</v>
       </c>
       <c r="S34" s="7" t="str">
-        <f>IF(R34="","ni opravljal izpita",IF(R34&lt;$U$3,"negativno",LOOKUP(R34,$U$3:$U$7,$V$3:$V$7)))</f>
+        <f t="shared" si="3"/>
         <v>negativno</v>
       </c>
       <c r="W34" s="5" t="s">
@@ -8314,19 +8310,19 @@
       </c>
       <c r="O35" s="3"/>
       <c r="P35" s="7">
-        <f>IF(COUNTBLANK(D35:M35)=10,"",SUM(D35:M35))</f>
+        <f t="shared" si="4"/>
         <v>18</v>
       </c>
       <c r="Q35" s="7">
-        <f>IF(COUNTBLANK(D35:O35)=12,"",MAX(N35+P35,O35+0.5*P35))</f>
+        <f t="shared" ref="Q35:Q66" si="13">IF(COUNTBLANK(D35:O35)=12,"",MAX(N35+P35,O35+0.5*P35))</f>
         <v>66</v>
       </c>
       <c r="R35" s="8">
-        <f>IF(COUNTBLANK(N35:O35)=2,"",IF(AND(SUM(N35:O35)=0,P35&lt;0),0,Q35/100))</f>
+        <f t="shared" ref="R35:R66" si="14">IF(COUNTBLANK(N35:O35)=2,"",IF(AND(SUM(N35:O35)=0,P35&lt;0),0,Q35/100))</f>
         <v>0.66</v>
       </c>
       <c r="S35" s="7">
-        <f>IF(R35="","ni opravljal izpita",IF(R35&lt;$U$3,"negativno",LOOKUP(R35,$U$3:$U$7,$V$3:$V$7)))</f>
+        <f t="shared" ref="S35:S66" si="15">IF(R35="","ni opravljal izpita",IF(R35&lt;$U$3,"negativno",LOOKUP(R35,$U$3:$U$7,$V$3:$V$7)))</f>
         <v>7</v>
       </c>
     </row>
@@ -8375,19 +8371,19 @@
         <v>45</v>
       </c>
       <c r="P36" s="7">
-        <f>IF(COUNTBLANK(D36:M36)=10,"",SUM(D36:M36))</f>
+        <f t="shared" si="4"/>
         <v>15</v>
       </c>
       <c r="Q36" s="7">
-        <f>IF(COUNTBLANK(D36:O36)=12,"",MAX(N36+P36,O36+0.5*P36))</f>
+        <f t="shared" si="13"/>
         <v>52.5</v>
       </c>
       <c r="R36" s="8">
-        <f>IF(COUNTBLANK(N36:O36)=2,"",IF(AND(SUM(N36:O36)=0,P36&lt;0),0,Q36/100))</f>
+        <f t="shared" si="14"/>
         <v>0.52500000000000002</v>
       </c>
       <c r="S36" s="7">
-        <f>IF(R36="","ni opravljal izpita",IF(R36&lt;$U$3,"negativno",LOOKUP(R36,$U$3:$U$7,$V$3:$V$7)))</f>
+        <f t="shared" si="15"/>
         <v>6</v>
       </c>
     </row>
@@ -8436,19 +8432,19 @@
       </c>
       <c r="O37" s="3"/>
       <c r="P37" s="7">
-        <f>IF(COUNTBLANK(D37:M37)=10,"",SUM(D37:M37))</f>
+        <f t="shared" si="4"/>
         <v>16</v>
       </c>
       <c r="Q37" s="7">
-        <f>IF(COUNTBLANK(D37:O37)=12,"",MAX(N37+P37,O37+0.5*P37))</f>
+        <f t="shared" si="13"/>
         <v>42</v>
       </c>
       <c r="R37" s="8">
-        <f>IF(COUNTBLANK(N37:O37)=2,"",IF(AND(SUM(N37:O37)=0,P37&lt;0),0,Q37/100))</f>
+        <f t="shared" si="14"/>
         <v>0.42</v>
       </c>
       <c r="S37" s="7" t="str">
-        <f>IF(R37="","ni opravljal izpita",IF(R37&lt;$U$3,"negativno",LOOKUP(R37,$U$3:$U$7,$V$3:$V$7)))</f>
+        <f t="shared" si="15"/>
         <v>negativno</v>
       </c>
     </row>
@@ -8475,19 +8471,19 @@
       <c r="N38" s="3"/>
       <c r="O38" s="3"/>
       <c r="P38" s="7" t="str">
-        <f>IF(COUNTBLANK(D38:M38)=10,"",SUM(D38:M38))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="Q38" s="7" t="str">
-        <f>IF(COUNTBLANK(D38:O38)=12,"",MAX(N38+P38,O38+0.5*P38))</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="R38" s="8" t="str">
-        <f>IF(COUNTBLANK(N38:O38)=2,"",IF(AND(SUM(N38:O38)=0,P38&lt;0),0,Q38/100))</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="S38" s="7" t="str">
-        <f>IF(R38="","ni opravljal izpita",IF(R38&lt;$U$3,"negativno",LOOKUP(R38,$U$3:$U$7,$V$3:$V$7)))</f>
+        <f t="shared" si="15"/>
         <v>ni opravljal izpita</v>
       </c>
     </row>
@@ -8514,19 +8510,19 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="7" t="str">
-        <f>IF(COUNTBLANK(D39:M39)=10,"",SUM(D39:M39))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="Q39" s="7" t="str">
-        <f>IF(COUNTBLANK(D39:O39)=12,"",MAX(N39+P39,O39+0.5*P39))</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="R39" s="8" t="str">
-        <f>IF(COUNTBLANK(N39:O39)=2,"",IF(AND(SUM(N39:O39)=0,P39&lt;0),0,Q39/100))</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="S39" s="7" t="str">
-        <f>IF(R39="","ni opravljal izpita",IF(R39&lt;$U$3,"negativno",LOOKUP(R39,$U$3:$U$7,$V$3:$V$7)))</f>
+        <f t="shared" si="15"/>
         <v>ni opravljal izpita</v>
       </c>
     </row>
@@ -8565,19 +8561,19 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="7">
-        <f>IF(COUNTBLANK(D40:M40)=10,"",SUM(D40:M40))</f>
+        <f t="shared" si="4"/>
         <v>4</v>
       </c>
       <c r="Q40" s="7">
-        <f>IF(COUNTBLANK(D40:O40)=12,"",MAX(N40+P40,O40+0.5*P40))</f>
+        <f t="shared" si="13"/>
         <v>4</v>
       </c>
       <c r="R40" s="8" t="str">
-        <f>IF(COUNTBLANK(N40:O40)=2,"",IF(AND(SUM(N40:O40)=0,P40&lt;0),0,Q40/100))</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="S40" s="7" t="str">
-        <f>IF(R40="","ni opravljal izpita",IF(R40&lt;$U$3,"negativno",LOOKUP(R40,$U$3:$U$7,$V$3:$V$7)))</f>
+        <f t="shared" si="15"/>
         <v>ni opravljal izpita</v>
       </c>
     </row>
@@ -8606,19 +8602,19 @@
       <c r="N41" s="3"/>
       <c r="O41" s="3"/>
       <c r="P41" s="7">
-        <f>IF(COUNTBLANK(D41:M41)=10,"",SUM(D41:M41))</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="Q41" s="7">
-        <f>IF(COUNTBLANK(D41:O41)=12,"",MAX(N41+P41,O41+0.5*P41))</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="R41" s="8" t="str">
-        <f>IF(COUNTBLANK(N41:O41)=2,"",IF(AND(SUM(N41:O41)=0,P41&lt;0),0,Q41/100))</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="S41" s="7" t="str">
-        <f>IF(R41="","ni opravljal izpita",IF(R41&lt;$U$3,"negativno",LOOKUP(R41,$U$3:$U$7,$V$3:$V$7)))</f>
+        <f t="shared" si="15"/>
         <v>ni opravljal izpita</v>
       </c>
     </row>
@@ -8667,19 +8663,19 @@
       </c>
       <c r="O42" s="3"/>
       <c r="P42" s="7">
-        <f>IF(COUNTBLANK(D42:M42)=10,"",SUM(D42:M42))</f>
+        <f t="shared" si="4"/>
         <v>15</v>
       </c>
       <c r="Q42" s="7">
-        <f>IF(COUNTBLANK(D42:O42)=12,"",MAX(N42+P42,O42+0.5*P42))</f>
+        <f t="shared" si="13"/>
         <v>79</v>
       </c>
       <c r="R42" s="8">
-        <f>IF(COUNTBLANK(N42:O42)=2,"",IF(AND(SUM(N42:O42)=0,P42&lt;0),0,Q42/100))</f>
+        <f t="shared" si="14"/>
         <v>0.79</v>
       </c>
       <c r="S42" s="7">
-        <f>IF(R42="","ni opravljal izpita",IF(R42&lt;$U$3,"negativno",LOOKUP(R42,$U$3:$U$7,$V$3:$V$7)))</f>
+        <f t="shared" si="15"/>
         <v>8</v>
       </c>
     </row>
@@ -8724,19 +8720,19 @@
       </c>
       <c r="O43" s="3"/>
       <c r="P43" s="7">
-        <f>IF(COUNTBLANK(D43:M43)=10,"",SUM(D43:M43))</f>
+        <f t="shared" ref="P43:P74" si="16">IF(COUNTBLANK(D43:M43)=10,"",SUM(D43:M43))</f>
         <v>6</v>
       </c>
       <c r="Q43" s="7">
-        <f>IF(COUNTBLANK(D43:O43)=12,"",MAX(N43+P43,O43+0.5*P43))</f>
+        <f t="shared" si="13"/>
         <v>37</v>
       </c>
       <c r="R43" s="8">
-        <f>IF(COUNTBLANK(N43:O43)=2,"",IF(AND(SUM(N43:O43)=0,P43&lt;0),0,Q43/100))</f>
+        <f t="shared" si="14"/>
         <v>0.37</v>
       </c>
       <c r="S43" s="7" t="str">
-        <f>IF(R43="","ni opravljal izpita",IF(R43&lt;$U$3,"negativno",LOOKUP(R43,$U$3:$U$7,$V$3:$V$7)))</f>
+        <f t="shared" si="15"/>
         <v>negativno</v>
       </c>
     </row>
@@ -8775,19 +8771,19 @@
       </c>
       <c r="O44" s="3"/>
       <c r="P44" s="7">
-        <f>IF(COUNTBLANK(D44:M44)=10,"",SUM(D44:M44))</f>
+        <f t="shared" si="16"/>
         <v>6</v>
       </c>
       <c r="Q44" s="7">
-        <f>IF(COUNTBLANK(D44:O44)=12,"",MAX(N44+P44,O44+0.5*P44))</f>
+        <f t="shared" si="13"/>
         <v>72</v>
       </c>
       <c r="R44" s="8">
-        <f>IF(COUNTBLANK(N44:O44)=2,"",IF(AND(SUM(N44:O44)=0,P44&lt;0),0,Q44/100))</f>
+        <f t="shared" si="14"/>
         <v>0.72</v>
       </c>
       <c r="S44" s="7">
-        <f>IF(R44="","ni opravljal izpita",IF(R44&lt;$U$3,"negativno",LOOKUP(R44,$U$3:$U$7,$V$3:$V$7)))</f>
+        <f t="shared" si="15"/>
         <v>8</v>
       </c>
     </row>
@@ -8830,19 +8826,19 @@
       </c>
       <c r="O45" s="3"/>
       <c r="P45" s="7">
-        <f>IF(COUNTBLANK(D45:M45)=10,"",SUM(D45:M45))</f>
+        <f t="shared" si="16"/>
         <v>10</v>
       </c>
       <c r="Q45" s="7">
-        <f>IF(COUNTBLANK(D45:O45)=12,"",MAX(N45+P45,O45+0.5*P45))</f>
+        <f t="shared" si="13"/>
         <v>54</v>
       </c>
       <c r="R45" s="8">
-        <f>IF(COUNTBLANK(N45:O45)=2,"",IF(AND(SUM(N45:O45)=0,P45&lt;0),0,Q45/100))</f>
+        <f t="shared" si="14"/>
         <v>0.54</v>
       </c>
       <c r="S45" s="7">
-        <f>IF(R45="","ni opravljal izpita",IF(R45&lt;$U$3,"negativno",LOOKUP(R45,$U$3:$U$7,$V$3:$V$7)))</f>
+        <f t="shared" si="15"/>
         <v>6</v>
       </c>
     </row>
@@ -8887,19 +8883,19 @@
       </c>
       <c r="O46" s="3"/>
       <c r="P46" s="7">
-        <f>IF(COUNTBLANK(D46:M46)=10,"",SUM(D46:M46))</f>
+        <f t="shared" si="16"/>
         <v>10</v>
       </c>
       <c r="Q46" s="7">
-        <f>IF(COUNTBLANK(D46:O46)=12,"",MAX(N46+P46,O46+0.5*P46))</f>
+        <f t="shared" si="13"/>
         <v>20</v>
       </c>
       <c r="R46" s="8">
-        <f>IF(COUNTBLANK(N46:O46)=2,"",IF(AND(SUM(N46:O46)=0,P46&lt;0),0,Q46/100))</f>
+        <f t="shared" si="14"/>
         <v>0.2</v>
       </c>
       <c r="S46" s="7" t="str">
-        <f>IF(R46="","ni opravljal izpita",IF(R46&lt;$U$3,"negativno",LOOKUP(R46,$U$3:$U$7,$V$3:$V$7)))</f>
+        <f t="shared" si="15"/>
         <v>negativno</v>
       </c>
     </row>
@@ -8944,19 +8940,19 @@
       </c>
       <c r="O47" s="3"/>
       <c r="P47" s="7">
-        <f>IF(COUNTBLANK(D47:M47)=10,"",SUM(D47:M47))</f>
+        <f t="shared" si="16"/>
         <v>11</v>
       </c>
       <c r="Q47" s="7">
-        <f>IF(COUNTBLANK(D47:O47)=12,"",MAX(N47+P47,O47+0.5*P47))</f>
+        <f t="shared" si="13"/>
         <v>73</v>
       </c>
       <c r="R47" s="8">
-        <f>IF(COUNTBLANK(N47:O47)=2,"",IF(AND(SUM(N47:O47)=0,P47&lt;0),0,Q47/100))</f>
+        <f t="shared" si="14"/>
         <v>0.73</v>
       </c>
       <c r="S47" s="7">
-        <f>IF(R47="","ni opravljal izpita",IF(R47&lt;$U$3,"negativno",LOOKUP(R47,$U$3:$U$7,$V$3:$V$7)))</f>
+        <f t="shared" si="15"/>
         <v>8</v>
       </c>
     </row>
@@ -8999,19 +8995,19 @@
       <c r="N48" s="3"/>
       <c r="O48" s="3"/>
       <c r="P48" s="7">
-        <f>IF(COUNTBLANK(D48:M48)=10,"",SUM(D48:M48))</f>
+        <f t="shared" si="16"/>
         <v>3</v>
       </c>
       <c r="Q48" s="7">
-        <f>IF(COUNTBLANK(D48:O48)=12,"",MAX(N48+P48,O48+0.5*P48))</f>
+        <f t="shared" si="13"/>
         <v>3</v>
       </c>
       <c r="R48" s="8" t="str">
-        <f>IF(COUNTBLANK(N48:O48)=2,"",IF(AND(SUM(N48:O48)=0,P48&lt;0),0,Q48/100))</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="S48" s="7" t="str">
-        <f>IF(R48="","ni opravljal izpita",IF(R48&lt;$U$3,"negativno",LOOKUP(R48,$U$3:$U$7,$V$3:$V$7)))</f>
+        <f t="shared" si="15"/>
         <v>ni opravljal izpita</v>
       </c>
     </row>
@@ -9052,19 +9048,19 @@
         <v>28</v>
       </c>
       <c r="P49" s="7">
-        <f>IF(COUNTBLANK(D49:M49)=10,"",SUM(D49:M49))</f>
+        <f t="shared" si="16"/>
         <v>5</v>
       </c>
       <c r="Q49" s="7">
-        <f>IF(COUNTBLANK(D49:O49)=12,"",MAX(N49+P49,O49+0.5*P49))</f>
+        <f t="shared" si="13"/>
         <v>30.5</v>
       </c>
       <c r="R49" s="8">
-        <f>IF(COUNTBLANK(N49:O49)=2,"",IF(AND(SUM(N49:O49)=0,P49&lt;0),0,Q49/100))</f>
+        <f t="shared" si="14"/>
         <v>0.30499999999999999</v>
       </c>
       <c r="S49" s="7" t="str">
-        <f>IF(R49="","ni opravljal izpita",IF(R49&lt;$U$3,"negativno",LOOKUP(R49,$U$3:$U$7,$V$3:$V$7)))</f>
+        <f t="shared" si="15"/>
         <v>negativno</v>
       </c>
     </row>
@@ -9109,19 +9105,19 @@
       </c>
       <c r="O50" s="3"/>
       <c r="P50" s="7">
-        <f>IF(COUNTBLANK(D50:M50)=10,"",SUM(D50:M50))</f>
+        <f t="shared" si="16"/>
         <v>11</v>
       </c>
       <c r="Q50" s="7">
-        <f>IF(COUNTBLANK(D50:O50)=12,"",MAX(N50+P50,O50+0.5*P50))</f>
+        <f t="shared" si="13"/>
         <v>42</v>
       </c>
       <c r="R50" s="8">
-        <f>IF(COUNTBLANK(N50:O50)=2,"",IF(AND(SUM(N50:O50)=0,P50&lt;0),0,Q50/100))</f>
+        <f t="shared" si="14"/>
         <v>0.42</v>
       </c>
       <c r="S50" s="7" t="str">
-        <f>IF(R50="","ni opravljal izpita",IF(R50&lt;$U$3,"negativno",LOOKUP(R50,$U$3:$U$7,$V$3:$V$7)))</f>
+        <f t="shared" si="15"/>
         <v>negativno</v>
       </c>
     </row>
@@ -9170,19 +9166,19 @@
       </c>
       <c r="O51" s="3"/>
       <c r="P51" s="7">
-        <f>IF(COUNTBLANK(D51:M51)=10,"",SUM(D51:M51))</f>
+        <f t="shared" si="16"/>
         <v>16</v>
       </c>
       <c r="Q51" s="7">
-        <f>IF(COUNTBLANK(D51:O51)=12,"",MAX(N51+P51,O51+0.5*P51))</f>
+        <f t="shared" si="13"/>
         <v>39</v>
       </c>
       <c r="R51" s="8">
-        <f>IF(COUNTBLANK(N51:O51)=2,"",IF(AND(SUM(N51:O51)=0,P51&lt;0),0,Q51/100))</f>
+        <f t="shared" si="14"/>
         <v>0.39</v>
       </c>
       <c r="S51" s="7" t="str">
-        <f>IF(R51="","ni opravljal izpita",IF(R51&lt;$U$3,"negativno",LOOKUP(R51,$U$3:$U$7,$V$3:$V$7)))</f>
+        <f t="shared" si="15"/>
         <v>negativno</v>
       </c>
     </row>
@@ -9231,19 +9227,19 @@
         <v>58</v>
       </c>
       <c r="P52" s="7">
-        <f>IF(COUNTBLANK(D52:M52)=10,"",SUM(D52:M52))</f>
+        <f t="shared" si="16"/>
         <v>13</v>
       </c>
       <c r="Q52" s="7">
-        <f>IF(COUNTBLANK(D52:O52)=12,"",MAX(N52+P52,O52+0.5*P52))</f>
+        <f t="shared" si="13"/>
         <v>64.5</v>
       </c>
       <c r="R52" s="8">
-        <f>IF(COUNTBLANK(N52:O52)=2,"",IF(AND(SUM(N52:O52)=0,P52&lt;0),0,Q52/100))</f>
+        <f t="shared" si="14"/>
         <v>0.64500000000000002</v>
       </c>
       <c r="S52" s="7">
-        <f>IF(R52="","ni opravljal izpita",IF(R52&lt;$U$3,"negativno",LOOKUP(R52,$U$3:$U$7,$V$3:$V$7)))</f>
+        <f t="shared" si="15"/>
         <v>7</v>
       </c>
     </row>
@@ -9270,19 +9266,19 @@
       <c r="N53" s="3"/>
       <c r="O53" s="3"/>
       <c r="P53" s="7" t="str">
-        <f>IF(COUNTBLANK(D53:M53)=10,"",SUM(D53:M53))</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="Q53" s="7" t="str">
-        <f>IF(COUNTBLANK(D53:O53)=12,"",MAX(N53+P53,O53+0.5*P53))</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="R53" s="8" t="str">
-        <f>IF(COUNTBLANK(N53:O53)=2,"",IF(AND(SUM(N53:O53)=0,P53&lt;0),0,Q53/100))</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="S53" s="7" t="str">
-        <f>IF(R53="","ni opravljal izpita",IF(R53&lt;$U$3,"negativno",LOOKUP(R53,$U$3:$U$7,$V$3:$V$7)))</f>
+        <f t="shared" si="15"/>
         <v>ni opravljal izpita</v>
       </c>
     </row>
@@ -9323,19 +9319,19 @@
       </c>
       <c r="O54" s="3"/>
       <c r="P54" s="7">
-        <f>IF(COUNTBLANK(D54:M54)=10,"",SUM(D54:M54))</f>
+        <f t="shared" si="16"/>
         <v>4</v>
       </c>
       <c r="Q54" s="7">
-        <f>IF(COUNTBLANK(D54:O54)=12,"",MAX(N54+P54,O54+0.5*P54))</f>
+        <f t="shared" si="13"/>
         <v>14</v>
       </c>
       <c r="R54" s="8">
-        <f>IF(COUNTBLANK(N54:O54)=2,"",IF(AND(SUM(N54:O54)=0,P54&lt;0),0,Q54/100))</f>
+        <f t="shared" si="14"/>
         <v>0.14000000000000001</v>
       </c>
       <c r="S54" s="7" t="str">
-        <f>IF(R54="","ni opravljal izpita",IF(R54&lt;$U$3,"negativno",LOOKUP(R54,$U$3:$U$7,$V$3:$V$7)))</f>
+        <f t="shared" si="15"/>
         <v>negativno</v>
       </c>
     </row>
@@ -9384,19 +9380,19 @@
       </c>
       <c r="O55" s="3"/>
       <c r="P55" s="7">
-        <f>IF(COUNTBLANK(D55:M55)=10,"",SUM(D55:M55))</f>
+        <f t="shared" si="16"/>
         <v>14</v>
       </c>
       <c r="Q55" s="7">
-        <f>IF(COUNTBLANK(D55:O55)=12,"",MAX(N55+P55,O55+0.5*P55))</f>
+        <f t="shared" si="13"/>
         <v>61</v>
       </c>
       <c r="R55" s="8">
-        <f>IF(COUNTBLANK(N55:O55)=2,"",IF(AND(SUM(N55:O55)=0,P55&lt;0),0,Q55/100))</f>
+        <f t="shared" si="14"/>
         <v>0.61</v>
       </c>
       <c r="S55" s="7">
-        <f>IF(R55="","ni opravljal izpita",IF(R55&lt;$U$3,"negativno",LOOKUP(R55,$U$3:$U$7,$V$3:$V$7)))</f>
+        <f t="shared" si="15"/>
         <v>7</v>
       </c>
     </row>
@@ -9427,19 +9423,19 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="7">
-        <f>IF(COUNTBLANK(D56:M56)=10,"",SUM(D56:M56))</f>
+        <f t="shared" si="16"/>
         <v>2</v>
       </c>
       <c r="Q56" s="7">
-        <f>IF(COUNTBLANK(D56:O56)=12,"",MAX(N56+P56,O56+0.5*P56))</f>
+        <f t="shared" si="13"/>
         <v>2</v>
       </c>
       <c r="R56" s="8" t="str">
-        <f>IF(COUNTBLANK(N56:O56)=2,"",IF(AND(SUM(N56:O56)=0,P56&lt;0),0,Q56/100))</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="S56" s="7" t="str">
-        <f>IF(R56="","ni opravljal izpita",IF(R56&lt;$U$3,"negativno",LOOKUP(R56,$U$3:$U$7,$V$3:$V$7)))</f>
+        <f t="shared" si="15"/>
         <v>ni opravljal izpita</v>
       </c>
     </row>
@@ -9466,19 +9462,19 @@
       <c r="N57" s="3"/>
       <c r="O57" s="3"/>
       <c r="P57" s="7" t="str">
-        <f>IF(COUNTBLANK(D57:M57)=10,"",SUM(D57:M57))</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="Q57" s="7" t="str">
-        <f>IF(COUNTBLANK(D57:O57)=12,"",MAX(N57+P57,O57+0.5*P57))</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="R57" s="8" t="str">
-        <f>IF(COUNTBLANK(N57:O57)=2,"",IF(AND(SUM(N57:O57)=0,P57&lt;0),0,Q57/100))</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="S57" s="7" t="str">
-        <f>IF(R57="","ni opravljal izpita",IF(R57&lt;$U$3,"negativno",LOOKUP(R57,$U$3:$U$7,$V$3:$V$7)))</f>
+        <f t="shared" si="15"/>
         <v>ni opravljal izpita</v>
       </c>
     </row>
@@ -9515,19 +9511,19 @@
       <c r="N58" s="3"/>
       <c r="O58" s="3"/>
       <c r="P58" s="7">
-        <f>IF(COUNTBLANK(D58:M58)=10,"",SUM(D58:M58))</f>
+        <f t="shared" si="16"/>
         <v>6</v>
       </c>
       <c r="Q58" s="7">
-        <f>IF(COUNTBLANK(D58:O58)=12,"",MAX(N58+P58,O58+0.5*P58))</f>
+        <f t="shared" si="13"/>
         <v>6</v>
       </c>
       <c r="R58" s="8" t="str">
-        <f>IF(COUNTBLANK(N58:O58)=2,"",IF(AND(SUM(N58:O58)=0,P58&lt;0),0,Q58/100))</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="S58" s="7" t="str">
-        <f>IF(R58="","ni opravljal izpita",IF(R58&lt;$U$3,"negativno",LOOKUP(R58,$U$3:$U$7,$V$3:$V$7)))</f>
+        <f t="shared" si="15"/>
         <v>ni opravljal izpita</v>
       </c>
     </row>
@@ -9576,19 +9572,19 @@
       </c>
       <c r="O59" s="3"/>
       <c r="P59" s="7">
-        <f>IF(COUNTBLANK(D59:M59)=10,"",SUM(D59:M59))</f>
+        <f t="shared" si="16"/>
         <v>13</v>
       </c>
       <c r="Q59" s="7">
-        <f>IF(COUNTBLANK(D59:O59)=12,"",MAX(N59+P59,O59+0.5*P59))</f>
+        <f t="shared" si="13"/>
         <v>70</v>
       </c>
       <c r="R59" s="8">
-        <f>IF(COUNTBLANK(N59:O59)=2,"",IF(AND(SUM(N59:O59)=0,P59&lt;0),0,Q59/100))</f>
+        <f t="shared" si="14"/>
         <v>0.7</v>
       </c>
       <c r="S59" s="7">
-        <f>IF(R59="","ni opravljal izpita",IF(R59&lt;$U$3,"negativno",LOOKUP(R59,$U$3:$U$7,$V$3:$V$7)))</f>
+        <f t="shared" si="15"/>
         <v>8</v>
       </c>
     </row>
@@ -9625,19 +9621,19 @@
       </c>
       <c r="O60" s="3"/>
       <c r="P60" s="7">
-        <f>IF(COUNTBLANK(D60:M60)=10,"",SUM(D60:M60))</f>
+        <f t="shared" si="16"/>
         <v>2</v>
       </c>
       <c r="Q60" s="7">
-        <f>IF(COUNTBLANK(D60:O60)=12,"",MAX(N60+P60,O60+0.5*P60))</f>
+        <f t="shared" si="13"/>
         <v>2</v>
       </c>
       <c r="R60" s="8">
-        <f>IF(COUNTBLANK(N60:O60)=2,"",IF(AND(SUM(N60:O60)=0,P60&lt;0),0,Q60/100))</f>
+        <f t="shared" si="14"/>
         <v>0.02</v>
       </c>
       <c r="S60" s="7" t="str">
-        <f>IF(R60="","ni opravljal izpita",IF(R60&lt;$U$3,"negativno",LOOKUP(R60,$U$3:$U$7,$V$3:$V$7)))</f>
+        <f t="shared" si="15"/>
         <v>negativno</v>
       </c>
     </row>
@@ -9666,19 +9662,19 @@
       <c r="N61" s="3"/>
       <c r="O61" s="3"/>
       <c r="P61" s="7">
-        <f>IF(COUNTBLANK(D61:M61)=10,"",SUM(D61:M61))</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="Q61" s="7">
-        <f>IF(COUNTBLANK(D61:O61)=12,"",MAX(N61+P61,O61+0.5*P61))</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="R61" s="8" t="str">
-        <f>IF(COUNTBLANK(N61:O61)=2,"",IF(AND(SUM(N61:O61)=0,P61&lt;0),0,Q61/100))</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="S61" s="7" t="str">
-        <f>IF(R61="","ni opravljal izpita",IF(R61&lt;$U$3,"negativno",LOOKUP(R61,$U$3:$U$7,$V$3:$V$7)))</f>
+        <f t="shared" si="15"/>
         <v>ni opravljal izpita</v>
       </c>
     </row>
@@ -9705,19 +9701,19 @@
       <c r="N62" s="3"/>
       <c r="O62" s="3"/>
       <c r="P62" s="7" t="str">
-        <f>IF(COUNTBLANK(D62:M62)=10,"",SUM(D62:M62))</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="Q62" s="7" t="str">
-        <f>IF(COUNTBLANK(D62:O62)=12,"",MAX(N62+P62,O62+0.5*P62))</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="R62" s="8" t="str">
-        <f>IF(COUNTBLANK(N62:O62)=2,"",IF(AND(SUM(N62:O62)=0,P62&lt;0),0,Q62/100))</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="S62" s="7" t="str">
-        <f>IF(R62="","ni opravljal izpita",IF(R62&lt;$U$3,"negativno",LOOKUP(R62,$U$3:$U$7,$V$3:$V$7)))</f>
+        <f t="shared" si="15"/>
         <v>ni opravljal izpita</v>
       </c>
     </row>
@@ -9744,19 +9740,19 @@
       <c r="N63" s="3"/>
       <c r="O63" s="3"/>
       <c r="P63" s="7" t="str">
-        <f>IF(COUNTBLANK(D63:M63)=10,"",SUM(D63:M63))</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="Q63" s="7" t="str">
-        <f>IF(COUNTBLANK(D63:O63)=12,"",MAX(N63+P63,O63+0.5*P63))</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="R63" s="8" t="str">
-        <f>IF(COUNTBLANK(N63:O63)=2,"",IF(AND(SUM(N63:O63)=0,P63&lt;0),0,Q63/100))</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="S63" s="7" t="str">
-        <f>IF(R63="","ni opravljal izpita",IF(R63&lt;$U$3,"negativno",LOOKUP(R63,$U$3:$U$7,$V$3:$V$7)))</f>
+        <f t="shared" si="15"/>
         <v>ni opravljal izpita</v>
       </c>
     </row>
@@ -9801,19 +9797,19 @@
       </c>
       <c r="O64" s="3"/>
       <c r="P64" s="7">
-        <f>IF(COUNTBLANK(D64:M64)=10,"",SUM(D64:M64))</f>
+        <f t="shared" si="16"/>
         <v>15</v>
       </c>
       <c r="Q64" s="7">
-        <f>IF(COUNTBLANK(D64:O64)=12,"",MAX(N64+P64,O64+0.5*P64))</f>
+        <f t="shared" si="13"/>
         <v>69</v>
       </c>
       <c r="R64" s="8">
-        <f>IF(COUNTBLANK(N64:O64)=2,"",IF(AND(SUM(N64:O64)=0,P64&lt;0),0,Q64/100))</f>
+        <f t="shared" si="14"/>
         <v>0.69</v>
       </c>
       <c r="S64" s="7">
-        <f>IF(R64="","ni opravljal izpita",IF(R64&lt;$U$3,"negativno",LOOKUP(R64,$U$3:$U$7,$V$3:$V$7)))</f>
+        <f t="shared" si="15"/>
         <v>7</v>
       </c>
     </row>
@@ -9864,19 +9860,19 @@
         <v>52</v>
       </c>
       <c r="P65" s="7">
-        <f>IF(COUNTBLANK(D65:M65)=10,"",SUM(D65:M65))</f>
+        <f t="shared" si="16"/>
         <v>12</v>
       </c>
       <c r="Q65" s="7">
-        <f>IF(COUNTBLANK(D65:O65)=12,"",MAX(N65+P65,O65+0.5*P65))</f>
+        <f t="shared" si="13"/>
         <v>58</v>
       </c>
       <c r="R65" s="8">
-        <f>IF(COUNTBLANK(N65:O65)=2,"",IF(AND(SUM(N65:O65)=0,P65&lt;0),0,Q65/100))</f>
+        <f t="shared" si="14"/>
         <v>0.57999999999999996</v>
       </c>
       <c r="S65" s="7">
-        <f>IF(R65="","ni opravljal izpita",IF(R65&lt;$U$3,"negativno",LOOKUP(R65,$U$3:$U$7,$V$3:$V$7)))</f>
+        <f t="shared" si="15"/>
         <v>6</v>
       </c>
     </row>
@@ -9925,19 +9921,19 @@
       </c>
       <c r="O66" s="3"/>
       <c r="P66" s="7">
-        <f>IF(COUNTBLANK(D66:M66)=10,"",SUM(D66:M66))</f>
+        <f t="shared" si="16"/>
         <v>15</v>
       </c>
       <c r="Q66" s="7">
-        <f>IF(COUNTBLANK(D66:O66)=12,"",MAX(N66+P66,O66+0.5*P66))</f>
+        <f t="shared" si="13"/>
         <v>68</v>
       </c>
       <c r="R66" s="8">
-        <f>IF(COUNTBLANK(N66:O66)=2,"",IF(AND(SUM(N66:O66)=0,P66&lt;0),0,Q66/100))</f>
+        <f t="shared" si="14"/>
         <v>0.68</v>
       </c>
       <c r="S66" s="7">
-        <f>IF(R66="","ni opravljal izpita",IF(R66&lt;$U$3,"negativno",LOOKUP(R66,$U$3:$U$7,$V$3:$V$7)))</f>
+        <f t="shared" si="15"/>
         <v>7</v>
       </c>
     </row>
@@ -9978,19 +9974,19 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="7">
-        <f>IF(COUNTBLANK(D67:M67)=10,"",SUM(D67:M67))</f>
+        <f t="shared" si="16"/>
         <v>9</v>
       </c>
       <c r="Q67" s="7">
-        <f>IF(COUNTBLANK(D67:O67)=12,"",MAX(N67+P67,O67+0.5*P67))</f>
+        <f t="shared" ref="Q67:Q98" si="17">IF(COUNTBLANK(D67:O67)=12,"",MAX(N67+P67,O67+0.5*P67))</f>
         <v>9</v>
       </c>
       <c r="R67" s="8" t="str">
-        <f>IF(COUNTBLANK(N67:O67)=2,"",IF(AND(SUM(N67:O67)=0,P67&lt;0),0,Q67/100))</f>
+        <f t="shared" ref="R67:R98" si="18">IF(COUNTBLANK(N67:O67)=2,"",IF(AND(SUM(N67:O67)=0,P67&lt;0),0,Q67/100))</f>
         <v/>
       </c>
       <c r="S67" s="7" t="str">
-        <f>IF(R67="","ni opravljal izpita",IF(R67&lt;$U$3,"negativno",LOOKUP(R67,$U$3:$U$7,$V$3:$V$7)))</f>
+        <f t="shared" ref="S67:S98" si="19">IF(R67="","ni opravljal izpita",IF(R67&lt;$U$3,"negativno",LOOKUP(R67,$U$3:$U$7,$V$3:$V$7)))</f>
         <v>ni opravljal izpita</v>
       </c>
     </row>
@@ -10023,19 +10019,19 @@
       <c r="N68" s="3"/>
       <c r="O68" s="3"/>
       <c r="P68" s="7">
-        <f>IF(COUNTBLANK(D68:M68)=10,"",SUM(D68:M68))</f>
+        <f t="shared" si="16"/>
         <v>2</v>
       </c>
       <c r="Q68" s="7">
-        <f>IF(COUNTBLANK(D68:O68)=12,"",MAX(N68+P68,O68+0.5*P68))</f>
+        <f t="shared" si="17"/>
         <v>2</v>
       </c>
       <c r="R68" s="8" t="str">
-        <f>IF(COUNTBLANK(N68:O68)=2,"",IF(AND(SUM(N68:O68)=0,P68&lt;0),0,Q68/100))</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="S68" s="7" t="str">
-        <f>IF(R68="","ni opravljal izpita",IF(R68&lt;$U$3,"negativno",LOOKUP(R68,$U$3:$U$7,$V$3:$V$7)))</f>
+        <f t="shared" si="19"/>
         <v>ni opravljal izpita</v>
       </c>
     </row>
@@ -10070,19 +10066,19 @@
       </c>
       <c r="O69" s="3"/>
       <c r="P69" s="7">
-        <f>IF(COUNTBLANK(D69:M69)=10,"",SUM(D69:M69))</f>
+        <f t="shared" si="16"/>
         <v>2</v>
       </c>
       <c r="Q69" s="7">
-        <f>IF(COUNTBLANK(D69:O69)=12,"",MAX(N69+P69,O69+0.5*P69))</f>
+        <f t="shared" si="17"/>
         <v>5</v>
       </c>
       <c r="R69" s="8">
-        <f>IF(COUNTBLANK(N69:O69)=2,"",IF(AND(SUM(N69:O69)=0,P69&lt;0),0,Q69/100))</f>
+        <f t="shared" si="18"/>
         <v>0.05</v>
       </c>
       <c r="S69" s="7" t="str">
-        <f>IF(R69="","ni opravljal izpita",IF(R69&lt;$U$3,"negativno",LOOKUP(R69,$U$3:$U$7,$V$3:$V$7)))</f>
+        <f t="shared" si="19"/>
         <v>negativno</v>
       </c>
     </row>
@@ -10133,19 +10129,19 @@
         <v>46</v>
       </c>
       <c r="P70" s="7">
-        <f>IF(COUNTBLANK(D70:M70)=10,"",SUM(D70:M70))</f>
+        <f t="shared" si="16"/>
         <v>15</v>
       </c>
       <c r="Q70" s="7">
-        <f>IF(COUNTBLANK(D70:O70)=12,"",MAX(N70+P70,O70+0.5*P70))</f>
+        <f t="shared" si="17"/>
         <v>53.5</v>
       </c>
       <c r="R70" s="8">
-        <f>IF(COUNTBLANK(N70:O70)=2,"",IF(AND(SUM(N70:O70)=0,P70&lt;0),0,Q70/100))</f>
+        <f t="shared" si="18"/>
         <v>0.53500000000000003</v>
       </c>
       <c r="S70" s="7">
-        <f>IF(R70="","ni opravljal izpita",IF(R70&lt;$U$3,"negativno",LOOKUP(R70,$U$3:$U$7,$V$3:$V$7)))</f>
+        <f t="shared" si="19"/>
         <v>6</v>
       </c>
     </row>
@@ -10188,19 +10184,19 @@
       </c>
       <c r="O71" s="3"/>
       <c r="P71" s="7">
-        <f>IF(COUNTBLANK(D71:M71)=10,"",SUM(D71:M71))</f>
+        <f t="shared" si="16"/>
         <v>5</v>
       </c>
       <c r="Q71" s="7">
-        <f>IF(COUNTBLANK(D71:O71)=12,"",MAX(N71+P71,O71+0.5*P71))</f>
+        <f t="shared" si="17"/>
         <v>49</v>
       </c>
       <c r="R71" s="8">
-        <f>IF(COUNTBLANK(N71:O71)=2,"",IF(AND(SUM(N71:O71)=0,P71&lt;0),0,Q71/100))</f>
+        <f t="shared" si="18"/>
         <v>0.49</v>
       </c>
       <c r="S71" s="7" t="str">
-        <f>IF(R71="","ni opravljal izpita",IF(R71&lt;$U$3,"negativno",LOOKUP(R71,$U$3:$U$7,$V$3:$V$7)))</f>
+        <f t="shared" si="19"/>
         <v>negativno</v>
       </c>
     </row>
@@ -10241,19 +10237,19 @@
         <v>20</v>
       </c>
       <c r="P72" s="7">
-        <f>IF(COUNTBLANK(D72:M72)=10,"",SUM(D72:M72))</f>
+        <f t="shared" si="16"/>
         <v>4</v>
       </c>
       <c r="Q72" s="7">
-        <f>IF(COUNTBLANK(D72:O72)=12,"",MAX(N72+P72,O72+0.5*P72))</f>
+        <f t="shared" si="17"/>
         <v>24</v>
       </c>
       <c r="R72" s="8">
-        <f>IF(COUNTBLANK(N72:O72)=2,"",IF(AND(SUM(N72:O72)=0,P72&lt;0),0,Q72/100))</f>
+        <f t="shared" si="18"/>
         <v>0.24</v>
       </c>
       <c r="S72" s="7" t="str">
-        <f>IF(R72="","ni opravljal izpita",IF(R72&lt;$U$3,"negativno",LOOKUP(R72,$U$3:$U$7,$V$3:$V$7)))</f>
+        <f t="shared" si="19"/>
         <v>negativno</v>
       </c>
     </row>
@@ -10296,19 +10292,19 @@
       </c>
       <c r="O73" s="3"/>
       <c r="P73" s="7">
-        <f>IF(COUNTBLANK(D73:M73)=10,"",SUM(D73:M73))</f>
+        <f t="shared" si="16"/>
         <v>10</v>
       </c>
       <c r="Q73" s="7">
-        <f>IF(COUNTBLANK(D73:O73)=12,"",MAX(N73+P73,O73+0.5*P73))</f>
+        <f t="shared" si="17"/>
         <v>59</v>
       </c>
       <c r="R73" s="8">
-        <f>IF(COUNTBLANK(N73:O73)=2,"",IF(AND(SUM(N73:O73)=0,P73&lt;0),0,Q73/100))</f>
+        <f t="shared" si="18"/>
         <v>0.59</v>
       </c>
       <c r="S73" s="7">
-        <f>IF(R73="","ni opravljal izpita",IF(R73&lt;$U$3,"negativno",LOOKUP(R73,$U$3:$U$7,$V$3:$V$7)))</f>
+        <f t="shared" si="19"/>
         <v>6</v>
       </c>
     </row>
@@ -10357,19 +10353,19 @@
       </c>
       <c r="O74" s="3"/>
       <c r="P74" s="7">
-        <f>IF(COUNTBLANK(D74:M74)=10,"",SUM(D74:M74))</f>
+        <f t="shared" si="16"/>
         <v>20</v>
       </c>
       <c r="Q74" s="7">
-        <f>IF(COUNTBLANK(D74:O74)=12,"",MAX(N74+P74,O74+0.5*P74))</f>
+        <f t="shared" si="17"/>
         <v>96</v>
       </c>
       <c r="R74" s="8">
-        <f>IF(COUNTBLANK(N74:O74)=2,"",IF(AND(SUM(N74:O74)=0,P74&lt;0),0,Q74/100))</f>
+        <f t="shared" si="18"/>
         <v>0.96</v>
       </c>
       <c r="S74" s="7">
-        <f>IF(R74="","ni opravljal izpita",IF(R74&lt;$U$3,"negativno",LOOKUP(R74,$U$3:$U$7,$V$3:$V$7)))</f>
+        <f t="shared" si="19"/>
         <v>10</v>
       </c>
     </row>
@@ -10418,19 +10414,19 @@
         <v>75</v>
       </c>
       <c r="P75" s="7">
-        <f>IF(COUNTBLANK(D75:M75)=10,"",SUM(D75:M75))</f>
+        <f t="shared" ref="P75:P82" si="20">IF(COUNTBLANK(D75:M75)=10,"",SUM(D75:M75))</f>
         <v>13</v>
       </c>
       <c r="Q75" s="7">
-        <f>IF(COUNTBLANK(D75:O75)=12,"",MAX(N75+P75,O75+0.5*P75))</f>
+        <f t="shared" si="17"/>
         <v>81.5</v>
       </c>
       <c r="R75" s="8">
-        <f>IF(COUNTBLANK(N75:O75)=2,"",IF(AND(SUM(N75:O75)=0,P75&lt;0),0,Q75/100))</f>
+        <f t="shared" si="18"/>
         <v>0.81499999999999995</v>
       </c>
       <c r="S75" s="7">
-        <f>IF(R75="","ni opravljal izpita",IF(R75&lt;$U$3,"negativno",LOOKUP(R75,$U$3:$U$7,$V$3:$V$7)))</f>
+        <f t="shared" si="19"/>
         <v>9</v>
       </c>
     </row>
@@ -10469,19 +10465,19 @@
       <c r="N76" s="3"/>
       <c r="O76" s="3"/>
       <c r="P76" s="7">
-        <f>IF(COUNTBLANK(D76:M76)=10,"",SUM(D76:M76))</f>
+        <f t="shared" si="20"/>
         <v>7</v>
       </c>
       <c r="Q76" s="7">
-        <f>IF(COUNTBLANK(D76:O76)=12,"",MAX(N76+P76,O76+0.5*P76))</f>
+        <f t="shared" si="17"/>
         <v>7</v>
       </c>
       <c r="R76" s="8" t="str">
-        <f>IF(COUNTBLANK(N76:O76)=2,"",IF(AND(SUM(N76:O76)=0,P76&lt;0),0,Q76/100))</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="S76" s="7" t="str">
-        <f>IF(R76="","ni opravljal izpita",IF(R76&lt;$U$3,"negativno",LOOKUP(R76,$U$3:$U$7,$V$3:$V$7)))</f>
+        <f t="shared" si="19"/>
         <v>ni opravljal izpita</v>
       </c>
     </row>
@@ -10530,19 +10526,19 @@
       </c>
       <c r="O77" s="3"/>
       <c r="P77" s="7">
-        <f>IF(COUNTBLANK(D77:M77)=10,"",SUM(D77:M77))</f>
+        <f t="shared" si="20"/>
         <v>18</v>
       </c>
       <c r="Q77" s="7">
-        <f>IF(COUNTBLANK(D77:O77)=12,"",MAX(N77+P77,O77+0.5*P77))</f>
+        <f t="shared" si="17"/>
         <v>58</v>
       </c>
       <c r="R77" s="8">
-        <f>IF(COUNTBLANK(N77:O77)=2,"",IF(AND(SUM(N77:O77)=0,P77&lt;0),0,Q77/100))</f>
+        <f t="shared" si="18"/>
         <v>0.57999999999999996</v>
       </c>
       <c r="S77" s="7">
-        <f>IF(R77="","ni opravljal izpita",IF(R77&lt;$U$3,"negativno",LOOKUP(R77,$U$3:$U$7,$V$3:$V$7)))</f>
+        <f t="shared" si="19"/>
         <v>6</v>
       </c>
     </row>
@@ -10571,19 +10567,19 @@
       <c r="N78" s="3"/>
       <c r="O78" s="3"/>
       <c r="P78" s="7">
-        <f>IF(COUNTBLANK(D78:M78)=10,"",SUM(D78:M78))</f>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="Q78" s="7">
-        <f>IF(COUNTBLANK(D78:O78)=12,"",MAX(N78+P78,O78+0.5*P78))</f>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="R78" s="8" t="str">
-        <f>IF(COUNTBLANK(N78:O78)=2,"",IF(AND(SUM(N78:O78)=0,P78&lt;0),0,Q78/100))</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="S78" s="7" t="str">
-        <f>IF(R78="","ni opravljal izpita",IF(R78&lt;$U$3,"negativno",LOOKUP(R78,$U$3:$U$7,$V$3:$V$7)))</f>
+        <f t="shared" si="19"/>
         <v>ni opravljal izpita</v>
       </c>
     </row>
@@ -10632,19 +10628,19 @@
         <v>26</v>
       </c>
       <c r="P79" s="7">
-        <f>IF(COUNTBLANK(D79:M79)=10,"",SUM(D79:M79))</f>
+        <f t="shared" si="20"/>
         <v>6</v>
       </c>
       <c r="Q79" s="7">
-        <f>IF(COUNTBLANK(D79:O79)=12,"",MAX(N79+P79,O79+0.5*P79))</f>
+        <f t="shared" si="17"/>
         <v>29</v>
       </c>
       <c r="R79" s="8">
-        <f>IF(COUNTBLANK(N79:O79)=2,"",IF(AND(SUM(N79:O79)=0,P79&lt;0),0,Q79/100))</f>
+        <f t="shared" si="18"/>
         <v>0.28999999999999998</v>
       </c>
       <c r="S79" s="7" t="str">
-        <f>IF(R79="","ni opravljal izpita",IF(R79&lt;$U$3,"negativno",LOOKUP(R79,$U$3:$U$7,$V$3:$V$7)))</f>
+        <f t="shared" si="19"/>
         <v>negativno</v>
       </c>
     </row>
@@ -10679,18 +10675,18 @@
       <c r="N80" s="3"/>
       <c r="O80" s="3"/>
       <c r="P80" s="7">
-        <f>IF(COUNTBLANK(D80:M80)=10,"",SUM(D80:M80))</f>
+        <f t="shared" si="20"/>
         <v>7</v>
       </c>
       <c r="Q80" s="7">
         <v>5</v>
       </c>
       <c r="R80" s="8" t="str">
-        <f>IF(COUNTBLANK(N80:O80)=2,"",IF(AND(SUM(N80:O80)=0,P80&lt;0),0,Q80/100))</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="S80" s="7" t="str">
-        <f>IF(R80="","ni opravljal izpita",IF(R80&lt;$U$3,"negativno",LOOKUP(R80,$U$3:$U$7,$V$3:$V$7)))</f>
+        <f t="shared" si="19"/>
         <v>ni opravljal izpita</v>
       </c>
     </row>
@@ -10739,19 +10735,19 @@
         <v>40</v>
       </c>
       <c r="P81" s="7">
-        <f>IF(COUNTBLANK(D81:M81)=10,"",SUM(D81:M81))</f>
+        <f t="shared" si="20"/>
         <v>11</v>
       </c>
       <c r="Q81" s="7">
-        <f>IF(COUNTBLANK(D81:O81)=12,"",MAX(N81+P81,O81+0.5*P81))</f>
+        <f t="shared" ref="Q81:Q117" si="21">IF(COUNTBLANK(D81:O81)=12,"",MAX(N81+P81,O81+0.5*P81))</f>
         <v>45.5</v>
       </c>
       <c r="R81" s="8">
-        <f>IF(COUNTBLANK(N81:O81)=2,"",IF(AND(SUM(N81:O81)=0,P81&lt;0),0,Q81/100))</f>
+        <f t="shared" si="18"/>
         <v>0.45500000000000002</v>
       </c>
       <c r="S81" s="7" t="str">
-        <f>IF(R81="","ni opravljal izpita",IF(R81&lt;$U$3,"negativno",LOOKUP(R81,$U$3:$U$7,$V$3:$V$7)))</f>
+        <f t="shared" si="19"/>
         <v>negativno</v>
       </c>
     </row>
@@ -10800,19 +10796,19 @@
       </c>
       <c r="O82" s="3"/>
       <c r="P82" s="7">
-        <f>IF(COUNTBLANK(D82:M82)=10,"",SUM(D82:M82))</f>
+        <f t="shared" si="20"/>
         <v>14</v>
       </c>
       <c r="Q82" s="7">
-        <f>IF(COUNTBLANK(D82:O82)=12,"",MAX(N82+P82,O82+0.5*P82))</f>
+        <f t="shared" si="21"/>
         <v>69</v>
       </c>
       <c r="R82" s="8">
-        <f>IF(COUNTBLANK(N82:O82)=2,"",IF(AND(SUM(N82:O82)=0,P82&lt;0),0,Q82/100))</f>
+        <f t="shared" si="18"/>
         <v>0.69</v>
       </c>
       <c r="S82" s="7">
-        <f>IF(R82="","ni opravljal izpita",IF(R82&lt;$U$3,"negativno",LOOKUP(R82,$U$3:$U$7,$V$3:$V$7)))</f>
+        <f t="shared" si="19"/>
         <v>7</v>
       </c>
     </row>
@@ -10842,15 +10838,15 @@
       <c r="O83" s="3"/>
       <c r="P83" s="7"/>
       <c r="Q83" s="7">
-        <f>IF(COUNTBLANK(D83:O83)=12,"",MAX(N83+P83,O83+0.5*P83))</f>
+        <f t="shared" si="21"/>
         <v>35</v>
       </c>
       <c r="R83" s="8">
-        <f>IF(COUNTBLANK(N83:O83)=2,"",IF(AND(SUM(N83:O83)=0,P83&lt;0),0,Q83/100))</f>
+        <f t="shared" si="18"/>
         <v>0.35</v>
       </c>
       <c r="S83" s="7" t="str">
-        <f>IF(R83="","ni opravljal izpita",IF(R83&lt;$U$3,"negativno",LOOKUP(R83,$U$3:$U$7,$V$3:$V$7)))</f>
+        <f t="shared" si="19"/>
         <v>negativno</v>
       </c>
     </row>
@@ -10891,19 +10887,19 @@
       </c>
       <c r="O84" s="3"/>
       <c r="P84" s="7">
-        <f>IF(COUNTBLANK(D84:M84)=10,"",SUM(D84:M84))</f>
+        <f t="shared" ref="P84:P117" si="22">IF(COUNTBLANK(D84:M84)=10,"",SUM(D84:M84))</f>
         <v>8</v>
       </c>
       <c r="Q84" s="7">
-        <f>IF(COUNTBLANK(D84:O84)=12,"",MAX(N84+P84,O84+0.5*P84))</f>
+        <f t="shared" si="21"/>
         <v>32</v>
       </c>
       <c r="R84" s="8">
-        <f>IF(COUNTBLANK(N84:O84)=2,"",IF(AND(SUM(N84:O84)=0,P84&lt;0),0,Q84/100))</f>
+        <f t="shared" si="18"/>
         <v>0.32</v>
       </c>
       <c r="S84" s="7" t="str">
-        <f>IF(R84="","ni opravljal izpita",IF(R84&lt;$U$3,"negativno",LOOKUP(R84,$U$3:$U$7,$V$3:$V$7)))</f>
+        <f t="shared" si="19"/>
         <v>negativno</v>
       </c>
     </row>
@@ -10938,19 +10934,19 @@
       </c>
       <c r="O85" s="3"/>
       <c r="P85" s="7">
-        <f>IF(COUNTBLANK(D85:M85)=10,"",SUM(D85:M85))</f>
+        <f t="shared" si="22"/>
         <v>4</v>
       </c>
       <c r="Q85" s="7">
-        <f>IF(COUNTBLANK(D85:O85)=12,"",MAX(N85+P85,O85+0.5*P85))</f>
+        <f t="shared" si="21"/>
         <v>9</v>
       </c>
       <c r="R85" s="8">
-        <f>IF(COUNTBLANK(N85:O85)=2,"",IF(AND(SUM(N85:O85)=0,P85&lt;0),0,Q85/100))</f>
+        <f t="shared" si="18"/>
         <v>0.09</v>
       </c>
       <c r="S85" s="7" t="str">
-        <f>IF(R85="","ni opravljal izpita",IF(R85&lt;$U$3,"negativno",LOOKUP(R85,$U$3:$U$7,$V$3:$V$7)))</f>
+        <f t="shared" si="19"/>
         <v>negativno</v>
       </c>
     </row>
@@ -10999,19 +10995,19 @@
       </c>
       <c r="O86" s="3"/>
       <c r="P86" s="7">
-        <f>IF(COUNTBLANK(D86:M86)=10,"",SUM(D86:M86))</f>
+        <f t="shared" si="22"/>
         <v>17</v>
       </c>
       <c r="Q86" s="7">
-        <f>IF(COUNTBLANK(D86:O86)=12,"",MAX(N86+P86,O86+0.5*P86))</f>
+        <f t="shared" si="21"/>
         <v>54</v>
       </c>
       <c r="R86" s="8">
-        <f>IF(COUNTBLANK(N86:O86)=2,"",IF(AND(SUM(N86:O86)=0,P86&lt;0),0,Q86/100))</f>
+        <f t="shared" si="18"/>
         <v>0.54</v>
       </c>
       <c r="S86" s="7">
-        <f>IF(R86="","ni opravljal izpita",IF(R86&lt;$U$3,"negativno",LOOKUP(R86,$U$3:$U$7,$V$3:$V$7)))</f>
+        <f t="shared" si="19"/>
         <v>6</v>
       </c>
     </row>
@@ -11038,19 +11034,19 @@
       <c r="N87" s="3"/>
       <c r="O87" s="3"/>
       <c r="P87" s="7" t="str">
-        <f>IF(COUNTBLANK(D87:M87)=10,"",SUM(D87:M87))</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="Q87" s="7" t="str">
-        <f>IF(COUNTBLANK(D87:O87)=12,"",MAX(N87+P87,O87+0.5*P87))</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="R87" s="8" t="str">
-        <f>IF(COUNTBLANK(N87:O87)=2,"",IF(AND(SUM(N87:O87)=0,P87&lt;0),0,Q87/100))</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="S87" s="7" t="str">
-        <f>IF(R87="","ni opravljal izpita",IF(R87&lt;$U$3,"negativno",LOOKUP(R87,$U$3:$U$7,$V$3:$V$7)))</f>
+        <f t="shared" si="19"/>
         <v>ni opravljal izpita</v>
       </c>
     </row>
@@ -11095,19 +11091,19 @@
       </c>
       <c r="O88" s="3"/>
       <c r="P88" s="7">
-        <f>IF(COUNTBLANK(D88:M88)=10,"",SUM(D88:M88))</f>
+        <f t="shared" si="22"/>
         <v>11</v>
       </c>
       <c r="Q88" s="7">
-        <f>IF(COUNTBLANK(D88:O88)=12,"",MAX(N88+P88,O88+0.5*P88))</f>
+        <f t="shared" si="21"/>
         <v>84</v>
       </c>
       <c r="R88" s="8">
-        <f>IF(COUNTBLANK(N88:O88)=2,"",IF(AND(SUM(N88:O88)=0,P88&lt;0),0,Q88/100))</f>
+        <f t="shared" si="18"/>
         <v>0.84</v>
       </c>
       <c r="S88" s="7">
-        <f>IF(R88="","ni opravljal izpita",IF(R88&lt;$U$3,"negativno",LOOKUP(R88,$U$3:$U$7,$V$3:$V$7)))</f>
+        <f t="shared" si="19"/>
         <v>9</v>
       </c>
     </row>
@@ -11140,19 +11136,19 @@
       <c r="N89" s="3"/>
       <c r="O89" s="3"/>
       <c r="P89" s="7">
-        <f>IF(COUNTBLANK(D89:M89)=10,"",SUM(D89:M89))</f>
+        <f t="shared" si="22"/>
         <v>1</v>
       </c>
       <c r="Q89" s="7">
-        <f>IF(COUNTBLANK(D89:O89)=12,"",MAX(N89+P89,O89+0.5*P89))</f>
+        <f t="shared" si="21"/>
         <v>1</v>
       </c>
       <c r="R89" s="8" t="str">
-        <f>IF(COUNTBLANK(N89:O89)=2,"",IF(AND(SUM(N89:O89)=0,P89&lt;0),0,Q89/100))</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="S89" s="7" t="str">
-        <f>IF(R89="","ni opravljal izpita",IF(R89&lt;$U$3,"negativno",LOOKUP(R89,$U$3:$U$7,$V$3:$V$7)))</f>
+        <f t="shared" si="19"/>
         <v>ni opravljal izpita</v>
       </c>
     </row>
@@ -11195,19 +11191,19 @@
       </c>
       <c r="O90" s="3"/>
       <c r="P90" s="7">
-        <f>IF(COUNTBLANK(D90:M90)=10,"",SUM(D90:M90))</f>
+        <f t="shared" si="22"/>
         <v>5</v>
       </c>
       <c r="Q90" s="7">
-        <f>IF(COUNTBLANK(D90:O90)=12,"",MAX(N90+P90,O90+0.5*P90))</f>
+        <f t="shared" si="21"/>
         <v>15</v>
       </c>
       <c r="R90" s="8">
-        <f>IF(COUNTBLANK(N90:O90)=2,"",IF(AND(SUM(N90:O90)=0,P90&lt;0),0,Q90/100))</f>
+        <f t="shared" si="18"/>
         <v>0.15</v>
       </c>
       <c r="S90" s="7" t="str">
-        <f>IF(R90="","ni opravljal izpita",IF(R90&lt;$U$3,"negativno",LOOKUP(R90,$U$3:$U$7,$V$3:$V$7)))</f>
+        <f t="shared" si="19"/>
         <v>negativno</v>
       </c>
     </row>
@@ -11256,19 +11252,19 @@
       </c>
       <c r="O91" s="3"/>
       <c r="P91" s="7">
-        <f>IF(COUNTBLANK(D91:M91)=10,"",SUM(D91:M91))</f>
+        <f t="shared" si="22"/>
         <v>14</v>
       </c>
       <c r="Q91" s="7">
-        <f>IF(COUNTBLANK(D91:O91)=12,"",MAX(N91+P91,O91+0.5*P91))</f>
+        <f t="shared" si="21"/>
         <v>58</v>
       </c>
       <c r="R91" s="8">
-        <f>IF(COUNTBLANK(N91:O91)=2,"",IF(AND(SUM(N91:O91)=0,P91&lt;0),0,Q91/100))</f>
+        <f t="shared" si="18"/>
         <v>0.57999999999999996</v>
       </c>
       <c r="S91" s="7">
-        <f>IF(R91="","ni opravljal izpita",IF(R91&lt;$U$3,"negativno",LOOKUP(R91,$U$3:$U$7,$V$3:$V$7)))</f>
+        <f t="shared" si="19"/>
         <v>6</v>
       </c>
     </row>
@@ -11317,19 +11313,19 @@
       </c>
       <c r="O92" s="3"/>
       <c r="P92" s="7">
-        <f>IF(COUNTBLANK(D92:M92)=10,"",SUM(D92:M92))</f>
+        <f t="shared" si="22"/>
         <v>20</v>
       </c>
       <c r="Q92" s="7">
-        <f>IF(COUNTBLANK(D92:O92)=12,"",MAX(N92+P92,O92+0.5*P92))</f>
+        <f t="shared" si="21"/>
         <v>89</v>
       </c>
       <c r="R92" s="8">
-        <f>IF(COUNTBLANK(N92:O92)=2,"",IF(AND(SUM(N92:O92)=0,P92&lt;0),0,Q92/100))</f>
+        <f t="shared" si="18"/>
         <v>0.89</v>
       </c>
       <c r="S92" s="7">
-        <f>IF(R92="","ni opravljal izpita",IF(R92&lt;$U$3,"negativno",LOOKUP(R92,$U$3:$U$7,$V$3:$V$7)))</f>
+        <f t="shared" si="19"/>
         <v>9</v>
       </c>
     </row>
@@ -11380,19 +11376,19 @@
         <v>58</v>
       </c>
       <c r="P93" s="7">
-        <f>IF(COUNTBLANK(D93:M93)=10,"",SUM(D93:M93))</f>
+        <f t="shared" si="22"/>
         <v>20</v>
       </c>
       <c r="Q93" s="7">
-        <f>IF(COUNTBLANK(D93:O93)=12,"",MAX(N93+P93,O93+0.5*P93))</f>
+        <f t="shared" si="21"/>
         <v>68</v>
       </c>
       <c r="R93" s="8">
-        <f>IF(COUNTBLANK(N93:O93)=2,"",IF(AND(SUM(N93:O93)=0,P93&lt;0),0,Q93/100))</f>
+        <f t="shared" si="18"/>
         <v>0.68</v>
       </c>
       <c r="S93" s="7">
-        <f>IF(R93="","ni opravljal izpita",IF(R93&lt;$U$3,"negativno",LOOKUP(R93,$U$3:$U$7,$V$3:$V$7)))</f>
+        <f t="shared" si="19"/>
         <v>7</v>
       </c>
     </row>
@@ -11423,19 +11419,19 @@
       </c>
       <c r="O94" s="3"/>
       <c r="P94" s="7">
-        <f>IF(COUNTBLANK(D94:M94)=10,"",SUM(D94:M94))</f>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="Q94" s="7">
-        <f>IF(COUNTBLANK(D94:O94)=12,"",MAX(N94+P94,O94+0.5*P94))</f>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="R94" s="8">
-        <f>IF(COUNTBLANK(N94:O94)=2,"",IF(AND(SUM(N94:O94)=0,P94&lt;0),0,Q94/100))</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="S94" s="7" t="str">
-        <f>IF(R94="","ni opravljal izpita",IF(R94&lt;$U$3,"negativno",LOOKUP(R94,$U$3:$U$7,$V$3:$V$7)))</f>
+        <f t="shared" si="19"/>
         <v>negativno</v>
       </c>
     </row>
@@ -11462,19 +11458,19 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="7" t="str">
-        <f>IF(COUNTBLANK(D95:M95)=10,"",SUM(D95:M95))</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="Q95" s="7" t="str">
-        <f>IF(COUNTBLANK(D95:O95)=12,"",MAX(N95+P95,O95+0.5*P95))</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="R95" s="8" t="str">
-        <f>IF(COUNTBLANK(N95:O95)=2,"",IF(AND(SUM(N95:O95)=0,P95&lt;0),0,Q95/100))</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="S95" s="7" t="str">
-        <f>IF(R95="","ni opravljal izpita",IF(R95&lt;$U$3,"negativno",LOOKUP(R95,$U$3:$U$7,$V$3:$V$7)))</f>
+        <f t="shared" si="19"/>
         <v>ni opravljal izpita</v>
       </c>
     </row>
@@ -11519,19 +11515,19 @@
       </c>
       <c r="O96" s="3"/>
       <c r="P96" s="7">
-        <f>IF(COUNTBLANK(D96:M96)=10,"",SUM(D96:M96))</f>
+        <f t="shared" si="22"/>
         <v>13</v>
       </c>
       <c r="Q96" s="7">
-        <f>IF(COUNTBLANK(D96:O96)=12,"",MAX(N96+P96,O96+0.5*P96))</f>
+        <f t="shared" si="21"/>
         <v>93</v>
       </c>
       <c r="R96" s="8">
-        <f>IF(COUNTBLANK(N96:O96)=2,"",IF(AND(SUM(N96:O96)=0,P96&lt;0),0,Q96/100))</f>
+        <f t="shared" si="18"/>
         <v>0.93</v>
       </c>
       <c r="S96" s="7">
-        <f>IF(R96="","ni opravljal izpita",IF(R96&lt;$U$3,"negativno",LOOKUP(R96,$U$3:$U$7,$V$3:$V$7)))</f>
+        <f t="shared" si="19"/>
         <v>10</v>
       </c>
     </row>
@@ -11578,19 +11574,19 @@
       </c>
       <c r="O97" s="3"/>
       <c r="P97" s="7">
-        <f>IF(COUNTBLANK(D97:M97)=10,"",SUM(D97:M97))</f>
+        <f t="shared" si="22"/>
         <v>12</v>
       </c>
       <c r="Q97" s="7">
-        <f>IF(COUNTBLANK(D97:O97)=12,"",MAX(N97+P97,O97+0.5*P97))</f>
+        <f t="shared" si="21"/>
         <v>61</v>
       </c>
       <c r="R97" s="8">
-        <f>IF(COUNTBLANK(N97:O97)=2,"",IF(AND(SUM(N97:O97)=0,P97&lt;0),0,Q97/100))</f>
+        <f t="shared" si="18"/>
         <v>0.61</v>
       </c>
       <c r="S97" s="7">
-        <f>IF(R97="","ni opravljal izpita",IF(R97&lt;$U$3,"negativno",LOOKUP(R97,$U$3:$U$7,$V$3:$V$7)))</f>
+        <f t="shared" si="19"/>
         <v>7</v>
       </c>
     </row>
@@ -11641,19 +11637,19 @@
         <v>55</v>
       </c>
       <c r="P98" s="7">
-        <f>IF(COUNTBLANK(D98:M98)=10,"",SUM(D98:M98))</f>
+        <f t="shared" si="22"/>
         <v>18</v>
       </c>
       <c r="Q98" s="7">
-        <f>IF(COUNTBLANK(D98:O98)=12,"",MAX(N98+P98,O98+0.5*P98))</f>
+        <f t="shared" si="21"/>
         <v>64</v>
       </c>
       <c r="R98" s="8">
-        <f>IF(COUNTBLANK(N98:O98)=2,"",IF(AND(SUM(N98:O98)=0,P98&lt;0),0,Q98/100))</f>
+        <f t="shared" si="18"/>
         <v>0.64</v>
       </c>
       <c r="S98" s="7">
-        <f>IF(R98="","ni opravljal izpita",IF(R98&lt;$U$3,"negativno",LOOKUP(R98,$U$3:$U$7,$V$3:$V$7)))</f>
+        <f t="shared" si="19"/>
         <v>7</v>
       </c>
     </row>
@@ -11702,19 +11698,19 @@
       </c>
       <c r="O99" s="3"/>
       <c r="P99" s="7">
-        <f>IF(COUNTBLANK(D99:M99)=10,"",SUM(D99:M99))</f>
+        <f t="shared" si="22"/>
         <v>12</v>
       </c>
       <c r="Q99" s="7">
-        <f>IF(COUNTBLANK(D99:O99)=12,"",MAX(N99+P99,O99+0.5*P99))</f>
+        <f t="shared" si="21"/>
         <v>40</v>
       </c>
       <c r="R99" s="8">
-        <f>IF(COUNTBLANK(N99:O99)=2,"",IF(AND(SUM(N99:O99)=0,P99&lt;0),0,Q99/100))</f>
+        <f t="shared" ref="R99:R130" si="23">IF(COUNTBLANK(N99:O99)=2,"",IF(AND(SUM(N99:O99)=0,P99&lt;0),0,Q99/100))</f>
         <v>0.4</v>
       </c>
       <c r="S99" s="7" t="str">
-        <f>IF(R99="","ni opravljal izpita",IF(R99&lt;$U$3,"negativno",LOOKUP(R99,$U$3:$U$7,$V$3:$V$7)))</f>
+        <f t="shared" ref="S99:S130" si="24">IF(R99="","ni opravljal izpita",IF(R99&lt;$U$3,"negativno",LOOKUP(R99,$U$3:$U$7,$V$3:$V$7)))</f>
         <v>negativno</v>
       </c>
     </row>
@@ -11741,19 +11737,19 @@
       <c r="N100" s="3"/>
       <c r="O100" s="3"/>
       <c r="P100" s="7" t="str">
-        <f>IF(COUNTBLANK(D100:M100)=10,"",SUM(D100:M100))</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="Q100" s="7" t="str">
-        <f>IF(COUNTBLANK(D100:O100)=12,"",MAX(N100+P100,O100+0.5*P100))</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="R100" s="8" t="str">
-        <f>IF(COUNTBLANK(N100:O100)=2,"",IF(AND(SUM(N100:O100)=0,P100&lt;0),0,Q100/100))</f>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="S100" s="7" t="str">
-        <f>IF(R100="","ni opravljal izpita",IF(R100&lt;$U$3,"negativno",LOOKUP(R100,$U$3:$U$7,$V$3:$V$7)))</f>
+        <f t="shared" si="24"/>
         <v>ni opravljal izpita</v>
       </c>
     </row>
@@ -11780,19 +11776,19 @@
       <c r="N101" s="3"/>
       <c r="O101" s="3"/>
       <c r="P101" s="7" t="str">
-        <f>IF(COUNTBLANK(D101:M101)=10,"",SUM(D101:M101))</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="Q101" s="7" t="str">
-        <f>IF(COUNTBLANK(D101:O101)=12,"",MAX(N101+P101,O101+0.5*P101))</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="R101" s="8" t="str">
-        <f>IF(COUNTBLANK(N101:O101)=2,"",IF(AND(SUM(N101:O101)=0,P101&lt;0),0,Q101/100))</f>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="S101" s="7" t="str">
-        <f>IF(R101="","ni opravljal izpita",IF(R101&lt;$U$3,"negativno",LOOKUP(R101,$U$3:$U$7,$V$3:$V$7)))</f>
+        <f t="shared" si="24"/>
         <v>ni opravljal izpita</v>
       </c>
     </row>
@@ -11839,19 +11835,19 @@
       </c>
       <c r="O102" s="3"/>
       <c r="P102" s="7">
-        <f>IF(COUNTBLANK(D102:M102)=10,"",SUM(D102:M102))</f>
+        <f t="shared" si="22"/>
         <v>1</v>
       </c>
       <c r="Q102" s="7">
-        <f>IF(COUNTBLANK(D102:O102)=12,"",MAX(N102+P102,O102+0.5*P102))</f>
+        <f t="shared" si="21"/>
         <v>1</v>
       </c>
       <c r="R102" s="8">
-        <f>IF(COUNTBLANK(N102:O102)=2,"",IF(AND(SUM(N102:O102)=0,P102&lt;0),0,Q102/100))</f>
+        <f t="shared" si="23"/>
         <v>0.01</v>
       </c>
       <c r="S102" s="7" t="str">
-        <f>IF(R102="","ni opravljal izpita",IF(R102&lt;$U$3,"negativno",LOOKUP(R102,$U$3:$U$7,$V$3:$V$7)))</f>
+        <f t="shared" si="24"/>
         <v>negativno</v>
       </c>
     </row>
@@ -11898,19 +11894,19 @@
       </c>
       <c r="O103" s="3"/>
       <c r="P103" s="7">
-        <f>IF(COUNTBLANK(D103:M103)=10,"",SUM(D103:M103))</f>
+        <f t="shared" si="22"/>
         <v>7</v>
       </c>
       <c r="Q103" s="7">
-        <f>IF(COUNTBLANK(D103:O103)=12,"",MAX(N103+P103,O103+0.5*P103))</f>
+        <f t="shared" si="21"/>
         <v>22</v>
       </c>
       <c r="R103" s="8">
-        <f>IF(COUNTBLANK(N103:O103)=2,"",IF(AND(SUM(N103:O103)=0,P103&lt;0),0,Q103/100))</f>
+        <f t="shared" si="23"/>
         <v>0.22</v>
       </c>
       <c r="S103" s="7" t="str">
-        <f>IF(R103="","ni opravljal izpita",IF(R103&lt;$U$3,"negativno",LOOKUP(R103,$U$3:$U$7,$V$3:$V$7)))</f>
+        <f t="shared" si="24"/>
         <v>negativno</v>
       </c>
     </row>
@@ -11953,19 +11949,19 @@
         <v>22</v>
       </c>
       <c r="P104" s="7">
-        <f>IF(COUNTBLANK(D104:M104)=10,"",SUM(D104:M104))</f>
+        <f t="shared" si="22"/>
         <v>6</v>
       </c>
       <c r="Q104" s="7">
-        <f>IF(COUNTBLANK(D104:O104)=12,"",MAX(N104+P104,O104+0.5*P104))</f>
+        <f t="shared" si="21"/>
         <v>25</v>
       </c>
       <c r="R104" s="8">
-        <f>IF(COUNTBLANK(N104:O104)=2,"",IF(AND(SUM(N104:O104)=0,P104&lt;0),0,Q104/100))</f>
+        <f t="shared" si="23"/>
         <v>0.25</v>
       </c>
       <c r="S104" s="7" t="str">
-        <f>IF(R104="","ni opravljal izpita",IF(R104&lt;$U$3,"negativno",LOOKUP(R104,$U$3:$U$7,$V$3:$V$7)))</f>
+        <f t="shared" si="24"/>
         <v>negativno</v>
       </c>
     </row>
@@ -12010,19 +12006,19 @@
       </c>
       <c r="O105" s="3"/>
       <c r="P105" s="7">
-        <f>IF(COUNTBLANK(D105:M105)=10,"",SUM(D105:M105))</f>
+        <f t="shared" si="22"/>
         <v>8</v>
       </c>
       <c r="Q105" s="7">
-        <f>IF(COUNTBLANK(D105:O105)=12,"",MAX(N105+P105,O105+0.5*P105))</f>
+        <f t="shared" si="21"/>
         <v>70</v>
       </c>
       <c r="R105" s="8">
-        <f>IF(COUNTBLANK(N105:O105)=2,"",IF(AND(SUM(N105:O105)=0,P105&lt;0),0,Q105/100))</f>
+        <f t="shared" si="23"/>
         <v>0.7</v>
       </c>
       <c r="S105" s="7">
-        <f>IF(R105="","ni opravljal izpita",IF(R105&lt;$U$3,"negativno",LOOKUP(R105,$U$3:$U$7,$V$3:$V$7)))</f>
+        <f t="shared" si="24"/>
         <v>8</v>
       </c>
     </row>
@@ -12071,19 +12067,19 @@
         <v>26</v>
       </c>
       <c r="P106" s="7">
-        <f>IF(COUNTBLANK(D106:M106)=10,"",SUM(D106:M106))</f>
+        <f t="shared" si="22"/>
         <v>7</v>
       </c>
       <c r="Q106" s="7">
-        <f>IF(COUNTBLANK(D106:O106)=12,"",MAX(N106+P106,O106+0.5*P106))</f>
+        <f t="shared" si="21"/>
         <v>29.5</v>
       </c>
       <c r="R106" s="8">
-        <f>IF(COUNTBLANK(N106:O106)=2,"",IF(AND(SUM(N106:O106)=0,P106&lt;0),0,Q106/100))</f>
+        <f t="shared" si="23"/>
         <v>0.29499999999999998</v>
       </c>
       <c r="S106" s="7" t="str">
-        <f>IF(R106="","ni opravljal izpita",IF(R106&lt;$U$3,"negativno",LOOKUP(R106,$U$3:$U$7,$V$3:$V$7)))</f>
+        <f t="shared" si="24"/>
         <v>negativno</v>
       </c>
     </row>
@@ -12130,19 +12126,19 @@
         <v>55</v>
       </c>
       <c r="P107" s="7">
-        <f>IF(COUNTBLANK(D107:M107)=10,"",SUM(D107:M107))</f>
+        <f t="shared" si="22"/>
         <v>15</v>
       </c>
       <c r="Q107" s="7">
-        <f>IF(COUNTBLANK(D107:O107)=12,"",MAX(N107+P107,O107+0.5*P107))</f>
+        <f t="shared" si="21"/>
         <v>63</v>
       </c>
       <c r="R107" s="8">
-        <f>IF(COUNTBLANK(N107:O107)=2,"",IF(AND(SUM(N107:O107)=0,P107&lt;0),0,Q107/100))</f>
+        <f t="shared" si="23"/>
         <v>0.63</v>
       </c>
       <c r="S107" s="7">
-        <f>IF(R107="","ni opravljal izpita",IF(R107&lt;$U$3,"negativno",LOOKUP(R107,$U$3:$U$7,$V$3:$V$7)))</f>
+        <f t="shared" si="24"/>
         <v>7</v>
       </c>
     </row>
@@ -12193,19 +12189,19 @@
         <v>64</v>
       </c>
       <c r="P108" s="7">
-        <f>IF(COUNTBLANK(D108:M108)=10,"",SUM(D108:M108))</f>
+        <f t="shared" si="22"/>
         <v>15</v>
       </c>
       <c r="Q108" s="7">
-        <f>IF(COUNTBLANK(D108:O108)=12,"",MAX(N108+P108,O108+0.5*P108))</f>
+        <f t="shared" si="21"/>
         <v>71.5</v>
       </c>
       <c r="R108" s="8">
-        <f>IF(COUNTBLANK(N108:O108)=2,"",IF(AND(SUM(N108:O108)=0,P108&lt;0),0,Q108/100))</f>
+        <f t="shared" si="23"/>
         <v>0.71499999999999997</v>
       </c>
       <c r="S108" s="7">
-        <f>IF(R108="","ni opravljal izpita",IF(R108&lt;$U$3,"negativno",LOOKUP(R108,$U$3:$U$7,$V$3:$V$7)))</f>
+        <f t="shared" si="24"/>
         <v>8</v>
       </c>
     </row>
@@ -12252,19 +12248,19 @@
       </c>
       <c r="O109" s="3"/>
       <c r="P109" s="7">
-        <f>IF(COUNTBLANK(D109:M109)=10,"",SUM(D109:M109))</f>
+        <f t="shared" si="22"/>
         <v>7</v>
       </c>
       <c r="Q109" s="7">
-        <f>IF(COUNTBLANK(D109:O109)=12,"",MAX(N109+P109,O109+0.5*P109))</f>
+        <f t="shared" si="21"/>
         <v>59</v>
       </c>
       <c r="R109" s="8">
-        <f>IF(COUNTBLANK(N109:O109)=2,"",IF(AND(SUM(N109:O109)=0,P109&lt;0),0,Q109/100))</f>
+        <f t="shared" si="23"/>
         <v>0.59</v>
       </c>
       <c r="S109" s="7">
-        <f>IF(R109="","ni opravljal izpita",IF(R109&lt;$U$3,"negativno",LOOKUP(R109,$U$3:$U$7,$V$3:$V$7)))</f>
+        <f t="shared" si="24"/>
         <v>6</v>
       </c>
     </row>
@@ -12313,19 +12309,19 @@
         <v>65</v>
       </c>
       <c r="P110" s="7">
-        <f>IF(COUNTBLANK(D110:M110)=10,"",SUM(D110:M110))</f>
+        <f t="shared" si="22"/>
         <v>13</v>
       </c>
       <c r="Q110" s="7">
-        <f>IF(COUNTBLANK(D110:O110)=12,"",MAX(N110+P110,O110+0.5*P110))</f>
+        <f t="shared" si="21"/>
         <v>71.5</v>
       </c>
       <c r="R110" s="8">
-        <f>IF(COUNTBLANK(N110:O110)=2,"",IF(AND(SUM(N110:O110)=0,P110&lt;0),0,Q110/100))</f>
+        <f t="shared" si="23"/>
         <v>0.71499999999999997</v>
       </c>
       <c r="S110" s="7">
-        <f>IF(R110="","ni opravljal izpita",IF(R110&lt;$U$3,"negativno",LOOKUP(R110,$U$3:$U$7,$V$3:$V$7)))</f>
+        <f t="shared" si="24"/>
         <v>8</v>
       </c>
     </row>
@@ -12370,19 +12366,19 @@
         <v>53</v>
       </c>
       <c r="P111" s="7">
-        <f>IF(COUNTBLANK(D111:M111)=10,"",SUM(D111:M111))</f>
+        <f t="shared" si="22"/>
         <v>3</v>
       </c>
       <c r="Q111" s="7">
-        <f>IF(COUNTBLANK(D111:O111)=12,"",MAX(N111+P111,O111+0.5*P111))</f>
+        <f t="shared" si="21"/>
         <v>54.5</v>
       </c>
       <c r="R111" s="8">
-        <f>IF(COUNTBLANK(N111:O111)=2,"",IF(AND(SUM(N111:O111)=0,P111&lt;0),0,Q111/100))</f>
+        <f t="shared" si="23"/>
         <v>0.54500000000000004</v>
       </c>
       <c r="S111" s="7">
-        <f>IF(R111="","ni opravljal izpita",IF(R111&lt;$U$3,"negativno",LOOKUP(R111,$U$3:$U$7,$V$3:$V$7)))</f>
+        <f t="shared" si="24"/>
         <v>6</v>
       </c>
     </row>
@@ -12409,19 +12405,19 @@
       <c r="N112" s="3"/>
       <c r="O112" s="3"/>
       <c r="P112" s="7" t="str">
-        <f>IF(COUNTBLANK(D112:M112)=10,"",SUM(D112:M112))</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="Q112" s="7" t="str">
-        <f>IF(COUNTBLANK(D112:O112)=12,"",MAX(N112+P112,O112+0.5*P112))</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="R112" s="8" t="str">
-        <f>IF(COUNTBLANK(N112:O112)=2,"",IF(AND(SUM(N112:O112)=0,P112&lt;0),0,Q112/100))</f>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="S112" s="7" t="str">
-        <f>IF(R112="","ni opravljal izpita",IF(R112&lt;$U$3,"negativno",LOOKUP(R112,$U$3:$U$7,$V$3:$V$7)))</f>
+        <f t="shared" si="24"/>
         <v>ni opravljal izpita</v>
       </c>
     </row>
@@ -12470,19 +12466,19 @@
         <v>35</v>
       </c>
       <c r="P113" s="7">
-        <f>IF(COUNTBLANK(D113:M113)=10,"",SUM(D113:M113))</f>
+        <f t="shared" si="22"/>
         <v>5</v>
       </c>
       <c r="Q113" s="7">
-        <f>IF(COUNTBLANK(D113:O113)=12,"",MAX(N113+P113,O113+0.5*P113))</f>
+        <f t="shared" si="21"/>
         <v>37.5</v>
       </c>
       <c r="R113" s="8">
-        <f>IF(COUNTBLANK(N113:O113)=2,"",IF(AND(SUM(N113:O113)=0,P113&lt;0),0,Q113/100))</f>
+        <f t="shared" si="23"/>
         <v>0.375</v>
       </c>
       <c r="S113" s="7" t="str">
-        <f>IF(R113="","ni opravljal izpita",IF(R113&lt;$U$3,"negativno",LOOKUP(R113,$U$3:$U$7,$V$3:$V$7)))</f>
+        <f t="shared" si="24"/>
         <v>negativno</v>
       </c>
     </row>
@@ -12533,19 +12529,19 @@
         <v>65</v>
       </c>
       <c r="P114" s="7">
-        <f>IF(COUNTBLANK(D114:M114)=10,"",SUM(D114:M114))</f>
+        <f t="shared" si="22"/>
         <v>15</v>
       </c>
       <c r="Q114" s="7">
-        <f>IF(COUNTBLANK(D114:O114)=12,"",MAX(N114+P114,O114+0.5*P114))</f>
+        <f t="shared" si="21"/>
         <v>72.5</v>
       </c>
       <c r="R114" s="8">
-        <f>IF(COUNTBLANK(N114:O114)=2,"",IF(AND(SUM(N114:O114)=0,P114&lt;0),0,Q114/100))</f>
+        <f t="shared" si="23"/>
         <v>0.72499999999999998</v>
       </c>
       <c r="S114" s="7">
-        <f>IF(R114="","ni opravljal izpita",IF(R114&lt;$U$3,"negativno",LOOKUP(R114,$U$3:$U$7,$V$3:$V$7)))</f>
+        <f t="shared" si="24"/>
         <v>8</v>
       </c>
     </row>
@@ -12572,19 +12568,19 @@
       <c r="N115" s="3"/>
       <c r="O115" s="3"/>
       <c r="P115" s="7" t="str">
-        <f>IF(COUNTBLANK(D115:M115)=10,"",SUM(D115:M115))</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="Q115" s="7" t="str">
-        <f>IF(COUNTBLANK(D115:O115)=12,"",MAX(N115+P115,O115+0.5*P115))</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="R115" s="8" t="str">
-        <f>IF(COUNTBLANK(N115:O115)=2,"",IF(AND(SUM(N115:O115)=0,P115&lt;0),0,Q115/100))</f>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="S115" s="7" t="str">
-        <f>IF(R115="","ni opravljal izpita",IF(R115&lt;$U$3,"negativno",LOOKUP(R115,$U$3:$U$7,$V$3:$V$7)))</f>
+        <f t="shared" si="24"/>
         <v>ni opravljal izpita</v>
       </c>
     </row>
@@ -12611,19 +12607,19 @@
       <c r="N116" s="3"/>
       <c r="O116" s="3"/>
       <c r="P116" s="7" t="str">
-        <f>IF(COUNTBLANK(D116:M116)=10,"",SUM(D116:M116))</f>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="Q116" s="7" t="str">
-        <f>IF(COUNTBLANK(D116:O116)=12,"",MAX(N116+P116,O116+0.5*P116))</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="R116" s="8" t="str">
-        <f>IF(COUNTBLANK(N116:O116)=2,"",IF(AND(SUM(N116:O116)=0,P116&lt;0),0,Q116/100))</f>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="S116" s="7" t="str">
-        <f>IF(R116="","ni opravljal izpita",IF(R116&lt;$U$3,"negativno",LOOKUP(R116,$U$3:$U$7,$V$3:$V$7)))</f>
+        <f t="shared" si="24"/>
         <v>ni opravljal izpita</v>
       </c>
     </row>
@@ -12672,19 +12668,19 @@
       </c>
       <c r="O117" s="3"/>
       <c r="P117" s="7">
-        <f>IF(COUNTBLANK(D117:M117)=10,"",SUM(D117:M117))</f>
+        <f t="shared" si="22"/>
         <v>20</v>
       </c>
       <c r="Q117" s="7">
-        <f>IF(COUNTBLANK(D117:O117)=12,"",MAX(N117+P117,O117+0.5*P117))</f>
+        <f t="shared" si="21"/>
         <v>120</v>
       </c>
       <c r="R117" s="8">
-        <f>IF(COUNTBLANK(N117:O117)=2,"",IF(AND(SUM(N117:O117)=0,P117&lt;0),0,Q117/100))</f>
+        <f t="shared" si="23"/>
         <v>1.2</v>
       </c>
       <c r="S117" s="7">
-        <f>IF(R117="","ni opravljal izpita",IF(R117&lt;$U$3,"negativno",LOOKUP(R117,$U$3:$U$7,$V$3:$V$7)))</f>
+        <f t="shared" si="24"/>
         <v>10</v>
       </c>
     </row>
@@ -12694,67 +12690,67 @@
         <v>113</v>
       </c>
       <c r="D119" s="5">
-        <f t="shared" ref="D119:S119" si="8">AVERAGE(D3:D117)</f>
+        <f t="shared" ref="D119:S119" si="25">AVERAGE(D3:D117)</f>
         <v>1.4130434782608696</v>
       </c>
       <c r="E119" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="25"/>
         <v>1.2558139534883721</v>
       </c>
       <c r="F119" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="25"/>
         <v>1.3764705882352941</v>
       </c>
       <c r="G119" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="25"/>
         <v>1.0117647058823529</v>
       </c>
       <c r="H119" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="25"/>
         <v>1.7560975609756098</v>
       </c>
       <c r="I119" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="25"/>
         <v>0.5357142857142857</v>
       </c>
       <c r="J119" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="25"/>
         <v>0.97727272727272729</v>
       </c>
       <c r="K119" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="25"/>
         <v>1.180327868852459</v>
       </c>
       <c r="L119" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="25"/>
         <v>1.5074626865671641</v>
       </c>
       <c r="M119" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="25"/>
         <v>1.5625</v>
       </c>
       <c r="N119" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="25"/>
         <v>38.392405063291136</v>
       </c>
       <c r="O119" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="25"/>
         <v>41.53846153846154</v>
       </c>
       <c r="P119" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="25"/>
         <v>9.5979381443298966</v>
       </c>
       <c r="Q119" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="25"/>
         <v>43.005050505050505</v>
       </c>
       <c r="R119" s="11">
-        <f t="shared" si="8"/>
+        <f t="shared" si="25"/>
         <v>0.51401234567901255</v>
       </c>
       <c r="S119" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="25"/>
         <v>7.4130434782608692</v>
       </c>
     </row>
